--- a/research/traditional_assets/database/data/tunisia/tunisia_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_construction_supplies.xlsx
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1531,22 +1531,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1627885951062328</v>
+        <v>0.1625826622135734</v>
       </c>
       <c r="C2">
-        <v>426.0448639715839</v>
+        <v>423.1435378840558</v>
       </c>
       <c r="D2">
-        <v>422.8648639715839</v>
+        <v>423.6105378840558</v>
       </c>
       <c r="E2">
-        <v>-128.2</v>
+        <v>-124.553</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.647</v>
       </c>
       <c r="G2">
         <v>3.18</v>
@@ -1567,28 +1567,28 @@
         <v>46.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1834441</v>
       </c>
       <c r="N2">
-        <v>46.5</v>
+        <v>46.3165559</v>
       </c>
       <c r="O2">
-        <v>6.975</v>
+        <v>6.947483384999999</v>
       </c>
       <c r="P2">
-        <v>39.525</v>
+        <v>39.369072515</v>
       </c>
       <c r="Q2">
-        <v>57.025</v>
+        <v>56.869072515</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1627885951062328</v>
+        <v>0.1637930426399731</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7216307604550376</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>253.4832136874394</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1625826622135734</v>
+        <v>0.1623767293209141</v>
       </c>
       <c r="C3">
-        <v>423.1435378840558</v>
+        <v>420.2448462637436</v>
       </c>
       <c r="D3">
-        <v>423.6105378840558</v>
+        <v>424.3588462637435</v>
       </c>
       <c r="E3">
-        <v>-124.553</v>
+        <v>-120.906</v>
       </c>
       <c r="F3">
-        <v>3.647</v>
+        <v>7.294</v>
       </c>
       <c r="G3">
         <v>3.18</v>
@@ -1649,28 +1649,28 @@
         <v>46.5</v>
       </c>
       <c r="M3">
-        <v>0.1834441</v>
+        <v>0.3668881999999999</v>
       </c>
       <c r="N3">
-        <v>46.3165559</v>
+        <v>46.1331118</v>
       </c>
       <c r="O3">
-        <v>6.947483384999999</v>
+        <v>6.91996677</v>
       </c>
       <c r="P3">
-        <v>39.369072515</v>
+        <v>39.21314503</v>
       </c>
       <c r="Q3">
-        <v>56.869072515</v>
+        <v>56.71314503</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1637930426399731</v>
+        <v>0.1648179891029735</v>
       </c>
       <c r="T3">
-        <v>0.7216307604550376</v>
+        <v>0.7278992054325732</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>253.4832136874394</v>
+        <v>126.7416068437197</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1695,22 +1695,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1623767293209141</v>
+        <v>0.1621707964282547</v>
       </c>
       <c r="C4">
-        <v>420.2448462637436</v>
+        <v>417.3488030967198</v>
       </c>
       <c r="D4">
-        <v>424.3588462637435</v>
+        <v>425.1098030967198</v>
       </c>
       <c r="E4">
-        <v>-120.906</v>
+        <v>-117.259</v>
       </c>
       <c r="F4">
-        <v>7.294</v>
+        <v>10.941</v>
       </c>
       <c r="G4">
         <v>3.18</v>
@@ -1731,28 +1731,28 @@
         <v>46.5</v>
       </c>
       <c r="M4">
-        <v>0.3668881999999999</v>
+        <v>0.5503322999999999</v>
       </c>
       <c r="N4">
-        <v>46.1331118</v>
+        <v>45.9496677</v>
       </c>
       <c r="O4">
-        <v>6.91996677</v>
+        <v>6.892450155</v>
       </c>
       <c r="P4">
-        <v>39.21314503</v>
+        <v>39.057217545</v>
       </c>
       <c r="Q4">
-        <v>56.71314503</v>
+        <v>56.557217545</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1648179891029735</v>
+        <v>0.1658640684827368</v>
       </c>
       <c r="T4">
-        <v>0.7278992054325732</v>
+        <v>0.7342968966983052</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>126.7416068437197</v>
+        <v>84.49440456247982</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1777,22 +1777,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1621707964282547</v>
+        <v>0.1619648635355954</v>
       </c>
       <c r="C5">
-        <v>417.3488030967198</v>
+        <v>414.4554224682325</v>
       </c>
       <c r="D5">
-        <v>425.1098030967198</v>
+        <v>425.8634224682325</v>
       </c>
       <c r="E5">
-        <v>-117.259</v>
+        <v>-113.612</v>
       </c>
       <c r="F5">
-        <v>10.941</v>
+        <v>14.588</v>
       </c>
       <c r="G5">
         <v>3.18</v>
@@ -1813,28 +1813,28 @@
         <v>46.5</v>
       </c>
       <c r="M5">
-        <v>0.5503322999999999</v>
+        <v>0.7337763999999999</v>
       </c>
       <c r="N5">
-        <v>45.9496677</v>
+        <v>45.7662236</v>
       </c>
       <c r="O5">
-        <v>6.892450155</v>
+        <v>6.86493354</v>
       </c>
       <c r="P5">
-        <v>39.057217545</v>
+        <v>38.90129006</v>
       </c>
       <c r="Q5">
-        <v>56.557217545</v>
+        <v>56.40129006</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1658640684827368</v>
+        <v>0.1669319411829119</v>
       </c>
       <c r="T5">
-        <v>0.7342968966983052</v>
+        <v>0.7408278731987402</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>84.49440456247982</v>
+        <v>63.37080342185986</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1859,22 +1859,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1619648635355954</v>
+        <v>0.161758930642936</v>
       </c>
       <c r="C6">
-        <v>414.4554224682325</v>
+        <v>411.5647185635866</v>
       </c>
       <c r="D6">
-        <v>425.8634224682325</v>
+        <v>426.6197185635866</v>
       </c>
       <c r="E6">
-        <v>-113.612</v>
+        <v>-109.965</v>
       </c>
       <c r="F6">
-        <v>14.588</v>
+        <v>18.235</v>
       </c>
       <c r="G6">
         <v>3.18</v>
@@ -1895,28 +1895,28 @@
         <v>46.5</v>
       </c>
       <c r="M6">
-        <v>0.7337763999999999</v>
+        <v>0.9172204999999999</v>
       </c>
       <c r="N6">
-        <v>45.7662236</v>
+        <v>45.5827795</v>
       </c>
       <c r="O6">
-        <v>6.86493354</v>
+        <v>6.837416925</v>
       </c>
       <c r="P6">
-        <v>38.90129006</v>
+        <v>38.745362575</v>
       </c>
       <c r="Q6">
-        <v>56.40129006</v>
+        <v>56.245362575</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1669319411829119</v>
+        <v>0.1680222954136169</v>
       </c>
       <c r="T6">
-        <v>0.7408278731987402</v>
+        <v>0.7474963439412895</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.37080342185986</v>
+        <v>50.69664273748788</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.161758930642936</v>
+        <v>0.1615529977502766</v>
       </c>
       <c r="C7">
-        <v>411.5647185635866</v>
+        <v>408.6767056690339</v>
       </c>
       <c r="D7">
-        <v>426.6197185635866</v>
+        <v>427.3787056690339</v>
       </c>
       <c r="E7">
-        <v>-109.965</v>
+        <v>-106.318</v>
       </c>
       <c r="F7">
-        <v>18.235</v>
+        <v>21.882</v>
       </c>
       <c r="G7">
         <v>3.18</v>
@@ -1977,28 +1977,28 @@
         <v>46.5</v>
       </c>
       <c r="M7">
-        <v>0.9172204999999999</v>
+        <v>1.1006646</v>
       </c>
       <c r="N7">
-        <v>45.5827795</v>
+        <v>45.3993354</v>
       </c>
       <c r="O7">
-        <v>6.837416925</v>
+        <v>6.80990031</v>
       </c>
       <c r="P7">
-        <v>38.745362575</v>
+        <v>38.58943508999999</v>
       </c>
       <c r="Q7">
-        <v>56.245362575</v>
+        <v>56.08943508999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1680222954136169</v>
+        <v>0.1691358486705071</v>
       </c>
       <c r="T7">
-        <v>0.7474963439412895</v>
+        <v>0.7543066970400631</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>50.69664273748788</v>
+        <v>42.24720228123989</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2023,22 +2023,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1615529977502766</v>
+        <v>0.1613470648576173</v>
       </c>
       <c r="C8">
-        <v>408.6767056690339</v>
+        <v>405.7913981726718</v>
       </c>
       <c r="D8">
-        <v>427.3787056690339</v>
+        <v>428.1403981726718</v>
       </c>
       <c r="E8">
-        <v>-106.318</v>
+        <v>-102.671</v>
       </c>
       <c r="F8">
-        <v>21.882</v>
+        <v>25.529</v>
       </c>
       <c r="G8">
         <v>3.18</v>
@@ -2059,28 +2059,28 @@
         <v>46.5</v>
       </c>
       <c r="M8">
-        <v>1.1006646</v>
+        <v>1.2841087</v>
       </c>
       <c r="N8">
-        <v>45.3993354</v>
+        <v>45.2158913</v>
       </c>
       <c r="O8">
-        <v>6.80990031</v>
+        <v>6.782383695</v>
       </c>
       <c r="P8">
-        <v>38.58943508999999</v>
+        <v>38.433507605</v>
       </c>
       <c r="Q8">
-        <v>56.08943508999999</v>
+        <v>55.933507605</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1691358486705071</v>
+        <v>0.1702733493092659</v>
       </c>
       <c r="T8">
-        <v>0.7543066970400631</v>
+        <v>0.7612635093452622</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.24720228123991</v>
+        <v>36.21188766963421</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1613470648576173</v>
+        <v>0.161141131964958</v>
       </c>
       <c r="C9">
-        <v>405.791398172672</v>
+        <v>402.9088105653543</v>
       </c>
       <c r="D9">
-        <v>428.140398172672</v>
+        <v>428.9048105653542</v>
       </c>
       <c r="E9">
-        <v>-102.671</v>
+        <v>-99.02399999999999</v>
       </c>
       <c r="F9">
-        <v>25.529</v>
+        <v>29.176</v>
       </c>
       <c r="G9">
         <v>3.18</v>
@@ -2141,28 +2141,28 @@
         <v>46.5</v>
       </c>
       <c r="M9">
-        <v>1.2841087</v>
+        <v>1.4675528</v>
       </c>
       <c r="N9">
-        <v>45.2158913</v>
+        <v>45.0324472</v>
       </c>
       <c r="O9">
-        <v>6.782383695</v>
+        <v>6.754867079999999</v>
       </c>
       <c r="P9">
-        <v>38.433507605</v>
+        <v>38.27758012</v>
       </c>
       <c r="Q9">
-        <v>55.933507605</v>
+        <v>55.77758012</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1702733493092659</v>
+        <v>0.1714355782227804</v>
       </c>
       <c r="T9">
-        <v>0.7612635093452622</v>
+        <v>0.7683715567005742</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.2118876696342</v>
+        <v>31.68540171092993</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.161141131964958</v>
+        <v>0.1609351990722986</v>
       </c>
       <c r="C10">
-        <v>402.9088105653543</v>
+        <v>400.0289574416086</v>
       </c>
       <c r="D10">
-        <v>428.9048105653542</v>
+        <v>429.6719574416085</v>
       </c>
       <c r="E10">
-        <v>-99.02399999999999</v>
+        <v>-95.37699999999998</v>
       </c>
       <c r="F10">
-        <v>29.176</v>
+        <v>32.823</v>
       </c>
       <c r="G10">
         <v>3.18</v>
@@ -2223,28 +2223,28 @@
         <v>46.5</v>
       </c>
       <c r="M10">
-        <v>1.4675528</v>
+        <v>1.6509969</v>
       </c>
       <c r="N10">
-        <v>45.0324472</v>
+        <v>44.8490031</v>
       </c>
       <c r="O10">
-        <v>6.754867079999999</v>
+        <v>6.727350465</v>
       </c>
       <c r="P10">
-        <v>38.27758012</v>
+        <v>38.121652635</v>
       </c>
       <c r="Q10">
-        <v>55.77758012</v>
+        <v>55.621652635</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1714355782227804</v>
+        <v>0.1726233506288996</v>
       </c>
       <c r="T10">
-        <v>0.7683715567005742</v>
+        <v>0.775635824876882</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.68540171092993</v>
+        <v>28.1648015208266</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2269,22 +2269,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1609351990722986</v>
+        <v>0.1607292661796393</v>
       </c>
       <c r="C11">
-        <v>400.0289574416086</v>
+        <v>397.1518535005657</v>
       </c>
       <c r="D11">
-        <v>429.6719574416085</v>
+        <v>430.4418535005657</v>
       </c>
       <c r="E11">
-        <v>-95.37699999999998</v>
+        <v>-91.72999999999999</v>
       </c>
       <c r="F11">
-        <v>32.823</v>
+        <v>36.47</v>
       </c>
       <c r="G11">
         <v>3.18</v>
@@ -2305,28 +2305,28 @@
         <v>46.5</v>
       </c>
       <c r="M11">
-        <v>1.6509969</v>
+        <v>1.834441</v>
       </c>
       <c r="N11">
-        <v>44.8490031</v>
+        <v>44.665559</v>
       </c>
       <c r="O11">
-        <v>6.727350465</v>
+        <v>6.69983385</v>
       </c>
       <c r="P11">
-        <v>38.121652635</v>
+        <v>37.96572515</v>
       </c>
       <c r="Q11">
-        <v>55.621652635</v>
+        <v>55.46572515</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1726233506288996</v>
+        <v>0.173837517977377</v>
       </c>
       <c r="T11">
-        <v>0.775635824876882</v>
+        <v>0.7830615212348857</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.1648015208266</v>
+        <v>25.34832136874394</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1607292661796393</v>
+        <v>0.1605233332869799</v>
       </c>
       <c r="C12">
-        <v>397.1518535005657</v>
+        <v>394.2775135468992</v>
       </c>
       <c r="D12">
-        <v>430.4418535005657</v>
+        <v>431.2145135468992</v>
       </c>
       <c r="E12">
-        <v>-91.72999999999999</v>
+        <v>-88.083</v>
       </c>
       <c r="F12">
-        <v>36.47</v>
+        <v>40.117</v>
       </c>
       <c r="G12">
         <v>3.18</v>
@@ -2387,28 +2387,28 @@
         <v>46.5</v>
       </c>
       <c r="M12">
-        <v>1.834441</v>
+        <v>2.0178851</v>
       </c>
       <c r="N12">
-        <v>44.665559</v>
+        <v>44.4821149</v>
       </c>
       <c r="O12">
-        <v>6.69983385</v>
+        <v>6.672317235</v>
       </c>
       <c r="P12">
-        <v>37.96572515</v>
+        <v>37.809797665</v>
       </c>
       <c r="Q12">
-        <v>55.46572515</v>
+        <v>55.309797665</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.173837517977377</v>
+        <v>0.1750789699853707</v>
       </c>
       <c r="T12">
-        <v>0.7830615212348857</v>
+        <v>0.790654087173968</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.34832136874394</v>
+        <v>23.04392851703995</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1605233332869799</v>
+        <v>0.1603174003943206</v>
       </c>
       <c r="C13">
-        <v>394.2775135468992</v>
+        <v>391.4059524917724</v>
       </c>
       <c r="D13">
-        <v>431.2145135468992</v>
+        <v>431.9899524917724</v>
       </c>
       <c r="E13">
-        <v>-88.083</v>
+        <v>-84.43599999999999</v>
       </c>
       <c r="F13">
-        <v>40.117</v>
+        <v>43.764</v>
       </c>
       <c r="G13">
         <v>3.18</v>
@@ -2469,28 +2469,28 @@
         <v>46.5</v>
       </c>
       <c r="M13">
-        <v>2.0178851</v>
+        <v>2.2013292</v>
       </c>
       <c r="N13">
-        <v>44.4821149</v>
+        <v>44.2986708</v>
       </c>
       <c r="O13">
-        <v>6.672317235</v>
+        <v>6.644800620000001</v>
       </c>
       <c r="P13">
-        <v>37.809797665</v>
+        <v>37.65387018000001</v>
       </c>
       <c r="Q13">
-        <v>55.309797665</v>
+        <v>55.15387018000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1750789699853707</v>
+        <v>0.1763486368117279</v>
       </c>
       <c r="T13">
-        <v>0.790654087173968</v>
+        <v>0.7984192114298477</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.04392851703995</v>
+        <v>21.12360114061995</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1603174003943206</v>
+        <v>0.1601114675016612</v>
       </c>
       <c r="C14">
-        <v>391.4059524917724</v>
+        <v>388.5371853538</v>
       </c>
       <c r="D14">
-        <v>431.9899524917724</v>
+        <v>432.7681853538</v>
       </c>
       <c r="E14">
-        <v>-84.43599999999999</v>
+        <v>-80.78899999999999</v>
       </c>
       <c r="F14">
-        <v>43.764</v>
+        <v>47.411</v>
       </c>
       <c r="G14">
         <v>3.18</v>
@@ -2551,28 +2551,28 @@
         <v>46.5</v>
       </c>
       <c r="M14">
-        <v>2.2013292</v>
+        <v>2.3847733</v>
       </c>
       <c r="N14">
-        <v>44.2986708</v>
+        <v>44.1152267</v>
       </c>
       <c r="O14">
-        <v>6.644800620000001</v>
+        <v>6.617284005</v>
       </c>
       <c r="P14">
-        <v>37.65387018000001</v>
+        <v>37.497942695</v>
       </c>
       <c r="Q14">
-        <v>55.15387018000001</v>
+        <v>54.997942695</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1763486368117279</v>
+        <v>0.1776474913812198</v>
       </c>
       <c r="T14">
-        <v>0.7984192114298477</v>
+        <v>0.8063628442893107</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.12360114061995</v>
+        <v>19.49870874518765</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2597,22 +2597,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1601114675016612</v>
+        <v>0.1599055346090019</v>
       </c>
       <c r="C15">
-        <v>388.5371853538</v>
+        <v>385.6712272600165</v>
       </c>
       <c r="D15">
-        <v>432.7681853538</v>
+        <v>433.5492272600164</v>
       </c>
       <c r="E15">
-        <v>-80.78899999999999</v>
+        <v>-77.142</v>
       </c>
       <c r="F15">
-        <v>47.411</v>
+        <v>51.058</v>
       </c>
       <c r="G15">
         <v>3.18</v>
@@ -2633,28 +2633,28 @@
         <v>46.5</v>
       </c>
       <c r="M15">
-        <v>2.3847733</v>
+        <v>2.5682174</v>
       </c>
       <c r="N15">
-        <v>44.1152267</v>
+        <v>43.9317826</v>
       </c>
       <c r="O15">
-        <v>6.617284005</v>
+        <v>6.58976739</v>
       </c>
       <c r="P15">
-        <v>37.497942695</v>
+        <v>37.34201521</v>
       </c>
       <c r="Q15">
-        <v>54.997942695</v>
+        <v>54.84201521</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1776474913812198</v>
+        <v>0.1789765518709324</v>
       </c>
       <c r="T15">
-        <v>0.8063628442893107</v>
+        <v>0.8144912127966683</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.49870874518765</v>
+        <v>18.1059438348171</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1599055346090019</v>
+        <v>0.1596996017163425</v>
       </c>
       <c r="C16">
-        <v>385.6712272600165</v>
+        <v>382.8080934468555</v>
       </c>
       <c r="D16">
-        <v>433.5492272600164</v>
+        <v>434.3330934468555</v>
       </c>
       <c r="E16">
-        <v>-77.142</v>
+        <v>-73.49499999999998</v>
       </c>
       <c r="F16">
-        <v>51.058</v>
+        <v>54.70500000000001</v>
       </c>
       <c r="G16">
         <v>3.18</v>
@@ -2715,28 +2715,28 @@
         <v>46.5</v>
       </c>
       <c r="M16">
-        <v>2.5682174</v>
+        <v>2.7516615</v>
       </c>
       <c r="N16">
-        <v>43.9317826</v>
+        <v>43.7483385</v>
       </c>
       <c r="O16">
-        <v>6.58976739</v>
+        <v>6.562250775</v>
       </c>
       <c r="P16">
-        <v>37.34201521</v>
+        <v>37.186087725</v>
       </c>
       <c r="Q16">
-        <v>54.84201521</v>
+        <v>54.686087725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1789765518709324</v>
+        <v>0.1803368843721677</v>
       </c>
       <c r="T16">
-        <v>0.8144912127966683</v>
+        <v>0.8228108370336108</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.1059438348171</v>
+        <v>16.89888091249596</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1596996017163425</v>
+        <v>0.1594936688236832</v>
       </c>
       <c r="C17">
-        <v>382.8080934468555</v>
+        <v>379.9477992611424</v>
       </c>
       <c r="D17">
-        <v>434.3330934468555</v>
+        <v>435.1197992611424</v>
       </c>
       <c r="E17">
-        <v>-73.49499999999999</v>
+        <v>-69.84799999999998</v>
       </c>
       <c r="F17">
-        <v>54.705</v>
+        <v>58.352</v>
       </c>
       <c r="G17">
         <v>3.18</v>
@@ -2797,28 +2797,28 @@
         <v>46.5</v>
       </c>
       <c r="M17">
-        <v>2.7516615</v>
+        <v>2.9351056</v>
       </c>
       <c r="N17">
-        <v>43.7483385</v>
+        <v>43.5648944</v>
       </c>
       <c r="O17">
-        <v>6.562250775</v>
+        <v>6.53473416</v>
       </c>
       <c r="P17">
-        <v>37.186087725</v>
+        <v>37.03016024</v>
       </c>
       <c r="Q17">
-        <v>54.686087725</v>
+        <v>54.53016024</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1803368843721677</v>
+        <v>0.18172960574248</v>
       </c>
       <c r="T17">
-        <v>0.8228108370336108</v>
+        <v>0.8313285475619091</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.89888091249596</v>
+        <v>15.84270085546496</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2843,22 +2843,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1594936688236832</v>
+        <v>0.1592877359310238</v>
       </c>
       <c r="C18">
-        <v>379.9477992611424</v>
+        <v>377.0903601610942</v>
       </c>
       <c r="D18">
-        <v>435.1197992611424</v>
+        <v>435.9093601610942</v>
       </c>
       <c r="E18">
-        <v>-69.84799999999998</v>
+        <v>-66.20099999999999</v>
       </c>
       <c r="F18">
-        <v>58.352</v>
+        <v>61.999</v>
       </c>
       <c r="G18">
         <v>3.18</v>
@@ -2879,28 +2879,28 @@
         <v>46.5</v>
       </c>
       <c r="M18">
-        <v>2.9351056</v>
+        <v>3.1185497</v>
       </c>
       <c r="N18">
-        <v>43.5648944</v>
+        <v>43.3814503</v>
       </c>
       <c r="O18">
-        <v>6.53473416</v>
+        <v>6.507217545</v>
       </c>
       <c r="P18">
-        <v>37.03016024</v>
+        <v>36.87423275499999</v>
       </c>
       <c r="Q18">
-        <v>54.53016024</v>
+        <v>54.37423275499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.18172960574248</v>
+        <v>0.1831558866638841</v>
       </c>
       <c r="T18">
-        <v>0.8313285475619091</v>
+        <v>0.8400515041270338</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.84270085546496</v>
+        <v>14.91077727573173</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2925,22 +2925,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1592877359310238</v>
+        <v>0.1590818030383645</v>
       </c>
       <c r="C19">
-        <v>377.0903601610942</v>
+        <v>374.2357917173333</v>
       </c>
       <c r="D19">
-        <v>435.9093601610942</v>
+        <v>436.7017917173333</v>
       </c>
       <c r="E19">
-        <v>-66.20099999999999</v>
+        <v>-62.55399999999999</v>
       </c>
       <c r="F19">
-        <v>61.999</v>
+        <v>65.646</v>
       </c>
       <c r="G19">
         <v>3.18</v>
@@ -2961,28 +2961,28 @@
         <v>46.5</v>
       </c>
       <c r="M19">
-        <v>3.1185497</v>
+        <v>3.3019938</v>
       </c>
       <c r="N19">
-        <v>43.3814503</v>
+        <v>43.1980062</v>
       </c>
       <c r="O19">
-        <v>6.507217545</v>
+        <v>6.47970093</v>
       </c>
       <c r="P19">
-        <v>36.87423275499999</v>
+        <v>36.71830527</v>
       </c>
       <c r="Q19">
-        <v>54.37423275499999</v>
+        <v>54.21830527</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1831558866638841</v>
+        <v>0.1846169549248347</v>
       </c>
       <c r="T19">
-        <v>0.8400515041270338</v>
+        <v>0.8489872157303322</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.91077727573173</v>
+        <v>14.0824007604133</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3007,22 +3007,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1590818030383645</v>
+        <v>0.1588758701457051</v>
       </c>
       <c r="C20">
-        <v>374.2357917173333</v>
+        <v>371.38410961391</v>
       </c>
       <c r="D20">
-        <v>436.7017917173333</v>
+        <v>437.49710961391</v>
       </c>
       <c r="E20">
-        <v>-62.55399999999999</v>
+        <v>-58.907</v>
       </c>
       <c r="F20">
-        <v>65.646</v>
+        <v>69.29299999999999</v>
       </c>
       <c r="G20">
         <v>3.18</v>
@@ -3043,28 +3043,28 @@
         <v>46.5</v>
       </c>
       <c r="M20">
-        <v>3.3019938</v>
+        <v>3.4854379</v>
       </c>
       <c r="N20">
-        <v>43.1980062</v>
+        <v>43.0145621</v>
       </c>
       <c r="O20">
-        <v>6.47970093</v>
+        <v>6.452184314999999</v>
       </c>
       <c r="P20">
-        <v>36.71830527</v>
+        <v>36.562377785</v>
       </c>
       <c r="Q20">
-        <v>54.21830527</v>
+        <v>54.062377785</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1846169549248347</v>
+        <v>0.186114098945315</v>
       </c>
       <c r="T20">
-        <v>0.8489872157303322</v>
+        <v>0.8581435621880331</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.0824007604133</v>
+        <v>13.34122177302313</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3089,22 +3089,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1588758701457051</v>
+        <v>0.1589249372530458</v>
       </c>
       <c r="C21">
-        <v>371.38410961391</v>
+        <v>367.5473484687557</v>
       </c>
       <c r="D21">
-        <v>437.49710961391</v>
+        <v>437.3073484687557</v>
       </c>
       <c r="E21">
-        <v>-58.907</v>
+        <v>-55.25999999999999</v>
       </c>
       <c r="F21">
-        <v>69.29299999999999</v>
+        <v>72.94</v>
       </c>
       <c r="G21">
         <v>3.18</v>
@@ -3125,45 +3125,45 @@
         <v>46.5</v>
       </c>
       <c r="M21">
-        <v>3.4854379</v>
+        <v>3.778292</v>
       </c>
       <c r="N21">
-        <v>43.0145621</v>
+        <v>42.721708</v>
       </c>
       <c r="O21">
-        <v>6.452184314999999</v>
+        <v>6.408256199999999</v>
       </c>
       <c r="P21">
-        <v>36.562377785</v>
+        <v>36.3134518</v>
       </c>
       <c r="Q21">
-        <v>54.062377785</v>
+        <v>53.8134518</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.186114098945315</v>
+        <v>0.1876486715663072</v>
       </c>
       <c r="T21">
-        <v>0.8581435621880331</v>
+        <v>0.8675288173071766</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.34122177302313</v>
+        <v>12.30714830934189</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3171,22 +3171,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1589249372530458</v>
+        <v>0.1587317543603865</v>
       </c>
       <c r="C22">
-        <v>367.5473484687557</v>
+        <v>364.6484135195188</v>
       </c>
       <c r="D22">
-        <v>437.3073484687557</v>
+        <v>438.0554135195188</v>
       </c>
       <c r="E22">
-        <v>-55.25999999999999</v>
+        <v>-51.61299999999999</v>
       </c>
       <c r="F22">
-        <v>72.94</v>
+        <v>76.587</v>
       </c>
       <c r="G22">
         <v>3.18</v>
@@ -3207,28 +3207,28 @@
         <v>46.5</v>
       </c>
       <c r="M22">
-        <v>3.778292</v>
+        <v>3.9672066</v>
       </c>
       <c r="N22">
-        <v>42.721708</v>
+        <v>42.5327934</v>
       </c>
       <c r="O22">
-        <v>6.408256199999999</v>
+        <v>6.37991901</v>
       </c>
       <c r="P22">
-        <v>36.3134518</v>
+        <v>36.15287439</v>
       </c>
       <c r="Q22">
-        <v>53.8134518</v>
+        <v>53.65287439</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1876486715663072</v>
+        <v>0.1892220941270714</v>
       </c>
       <c r="T22">
-        <v>0.8675288173071766</v>
+        <v>0.8771516738217415</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.30714830934189</v>
+        <v>11.72109362794466</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3253,22 +3253,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1587317543603864</v>
+        <v>0.1585385714677271</v>
       </c>
       <c r="C23">
-        <v>364.648413519519</v>
+        <v>361.7520422602159</v>
       </c>
       <c r="D23">
-        <v>438.055413519519</v>
+        <v>438.8060422602159</v>
       </c>
       <c r="E23">
-        <v>-51.613</v>
+        <v>-47.96599999999999</v>
       </c>
       <c r="F23">
-        <v>76.58699999999999</v>
+        <v>80.23399999999999</v>
       </c>
       <c r="G23">
         <v>3.18</v>
@@ -3289,28 +3289,28 @@
         <v>46.5</v>
       </c>
       <c r="M23">
-        <v>3.967206599999999</v>
+        <v>4.156121199999999</v>
       </c>
       <c r="N23">
-        <v>42.5327934</v>
+        <v>42.3438788</v>
       </c>
       <c r="O23">
-        <v>6.37991901</v>
+        <v>6.35158182</v>
       </c>
       <c r="P23">
-        <v>36.15287439</v>
+        <v>35.99229698</v>
       </c>
       <c r="Q23">
-        <v>53.65287439</v>
+        <v>53.49229698</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1892220941270714</v>
+        <v>0.1908358608560604</v>
       </c>
       <c r="T23">
-        <v>0.8771516738217413</v>
+        <v>0.8870212702469361</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.72109362794466</v>
+        <v>11.18831664485627</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3335,22 +3335,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1585385714677271</v>
+        <v>0.1583453885750677</v>
       </c>
       <c r="C24">
-        <v>361.7520422602159</v>
+        <v>358.8582478924811</v>
       </c>
       <c r="D24">
-        <v>438.8060422602159</v>
+        <v>439.5592478924812</v>
       </c>
       <c r="E24">
-        <v>-47.96599999999999</v>
+        <v>-44.31899999999999</v>
       </c>
       <c r="F24">
-        <v>80.23399999999999</v>
+        <v>83.881</v>
       </c>
       <c r="G24">
         <v>3.18</v>
@@ -3371,28 +3371,28 @@
         <v>46.5</v>
       </c>
       <c r="M24">
-        <v>4.156121199999999</v>
+        <v>4.3450358</v>
       </c>
       <c r="N24">
-        <v>42.3438788</v>
+        <v>42.1549642</v>
       </c>
       <c r="O24">
-        <v>6.35158182</v>
+        <v>6.32324463</v>
       </c>
       <c r="P24">
-        <v>35.99229698</v>
+        <v>35.83171957</v>
       </c>
       <c r="Q24">
-        <v>53.49229698</v>
+        <v>53.33171957</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1908358608560604</v>
+        <v>0.1924915436039841</v>
       </c>
       <c r="T24">
-        <v>0.8870212702469361</v>
+        <v>0.8971472198260318</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.18831664485627</v>
+        <v>10.70186809507991</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3417,22 +3417,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1583453885750677</v>
+        <v>0.1581522056824084</v>
       </c>
       <c r="C25">
-        <v>358.8582478924811</v>
+        <v>355.9670437087473</v>
       </c>
       <c r="D25">
-        <v>439.5592478924812</v>
+        <v>440.3150437087473</v>
       </c>
       <c r="E25">
-        <v>-44.31899999999999</v>
+        <v>-40.67199999999998</v>
       </c>
       <c r="F25">
-        <v>83.881</v>
+        <v>87.52800000000001</v>
       </c>
       <c r="G25">
         <v>3.18</v>
@@ -3453,28 +3453,28 @@
         <v>46.5</v>
       </c>
       <c r="M25">
-        <v>4.3450358</v>
+        <v>4.5339504</v>
       </c>
       <c r="N25">
-        <v>42.1549642</v>
+        <v>41.9660496</v>
       </c>
       <c r="O25">
-        <v>6.32324463</v>
+        <v>6.294907439999999</v>
       </c>
       <c r="P25">
-        <v>35.83171957</v>
+        <v>35.67114216</v>
       </c>
       <c r="Q25">
-        <v>53.33171957</v>
+        <v>53.17114216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1924915436039841</v>
+        <v>0.1941907969505374</v>
       </c>
       <c r="T25">
-        <v>0.8971472198260318</v>
+        <v>0.9075396417624724</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.70186809507991</v>
+        <v>10.25595692445158</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3499,22 +3499,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1581522056824084</v>
+        <v>0.157959022789749</v>
       </c>
       <c r="C26">
-        <v>355.9670437087473</v>
+        <v>353.0784430930264</v>
       </c>
       <c r="D26">
-        <v>440.3150437087473</v>
+        <v>441.0734430930264</v>
       </c>
       <c r="E26">
-        <v>-40.672</v>
+        <v>-37.02499999999999</v>
       </c>
       <c r="F26">
-        <v>87.52799999999999</v>
+        <v>91.175</v>
       </c>
       <c r="G26">
         <v>3.18</v>
@@ -3535,28 +3535,28 @@
         <v>46.5</v>
       </c>
       <c r="M26">
-        <v>4.533950399999999</v>
+        <v>4.722865</v>
       </c>
       <c r="N26">
-        <v>41.9660496</v>
+        <v>41.777135</v>
       </c>
       <c r="O26">
-        <v>6.294907439999999</v>
+        <v>6.26657025</v>
       </c>
       <c r="P26">
-        <v>35.67114216</v>
+        <v>35.51056475</v>
       </c>
       <c r="Q26">
-        <v>53.17114216</v>
+        <v>53.01056475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1941907969505374</v>
+        <v>0.1959353637196654</v>
       </c>
       <c r="T26">
-        <v>0.9075396417624724</v>
+        <v>0.9182091949505511</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.25595692445158</v>
+        <v>9.845718647473515</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3581,22 +3581,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.157959022789749</v>
+        <v>0.1581415398970897</v>
       </c>
       <c r="C27">
-        <v>353.0784430930264</v>
+        <v>348.7148475306739</v>
       </c>
       <c r="D27">
-        <v>441.0734430930264</v>
+        <v>440.3568475306739</v>
       </c>
       <c r="E27">
-        <v>-37.02499999999999</v>
+        <v>-33.37799999999999</v>
       </c>
       <c r="F27">
-        <v>91.175</v>
+        <v>94.822</v>
       </c>
       <c r="G27">
         <v>3.18</v>
@@ -3617,45 +3617,45 @@
         <v>46.5</v>
       </c>
       <c r="M27">
-        <v>4.722865</v>
+        <v>5.072977</v>
       </c>
       <c r="N27">
-        <v>41.777135</v>
+        <v>41.427023</v>
       </c>
       <c r="O27">
-        <v>6.26657025</v>
+        <v>6.21405345</v>
       </c>
       <c r="P27">
-        <v>35.51056475</v>
+        <v>35.21296955</v>
       </c>
       <c r="Q27">
-        <v>53.01056475</v>
+        <v>52.71296955</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1959353637196654</v>
+        <v>0.1977270809420131</v>
       </c>
       <c r="T27">
-        <v>0.9182091949505511</v>
+        <v>0.9291671144410105</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.845718647473515</v>
+        <v>9.166215419466715</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1581415398970897</v>
+        <v>0.1579628070044303</v>
       </c>
       <c r="C28">
-        <v>348.7148475306739</v>
+        <v>345.7695618980612</v>
       </c>
       <c r="D28">
-        <v>440.3568475306739</v>
+        <v>441.0585618980612</v>
       </c>
       <c r="E28">
-        <v>-33.37799999999999</v>
+        <v>-29.73099999999998</v>
       </c>
       <c r="F28">
-        <v>94.822</v>
+        <v>98.46900000000001</v>
       </c>
       <c r="G28">
         <v>3.18</v>
@@ -3699,28 +3699,28 @@
         <v>46.5</v>
       </c>
       <c r="M28">
-        <v>5.072977</v>
+        <v>5.268091500000001</v>
       </c>
       <c r="N28">
-        <v>41.427023</v>
+        <v>41.2319085</v>
       </c>
       <c r="O28">
-        <v>6.21405345</v>
+        <v>6.184786275</v>
       </c>
       <c r="P28">
-        <v>35.21296955</v>
+        <v>35.047122225</v>
       </c>
       <c r="Q28">
-        <v>52.71296955</v>
+        <v>52.547122225</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1977270809420131</v>
+        <v>0.1995678863074388</v>
       </c>
       <c r="T28">
-        <v>0.9291671144410105</v>
+        <v>0.9404252509038113</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.166215419466715</v>
+        <v>8.826725959486467</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1579628070044303</v>
+        <v>0.157784074111771</v>
       </c>
       <c r="C29">
-        <v>345.7695618980612</v>
+        <v>342.8265162167933</v>
       </c>
       <c r="D29">
-        <v>441.0585618980612</v>
+        <v>441.7625162167932</v>
       </c>
       <c r="E29">
-        <v>-29.73099999999998</v>
+        <v>-26.08399999999999</v>
       </c>
       <c r="F29">
-        <v>98.46900000000001</v>
+        <v>102.116</v>
       </c>
       <c r="G29">
         <v>3.18</v>
@@ -3781,28 +3781,28 @@
         <v>46.5</v>
       </c>
       <c r="M29">
-        <v>5.268091500000001</v>
+        <v>5.463206</v>
       </c>
       <c r="N29">
-        <v>41.2319085</v>
+        <v>41.036794</v>
       </c>
       <c r="O29">
-        <v>6.184786275</v>
+        <v>6.1555191</v>
       </c>
       <c r="P29">
-        <v>35.047122225</v>
+        <v>34.8812749</v>
       </c>
       <c r="Q29">
-        <v>52.547122225</v>
+        <v>52.3812749</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1995678863074388</v>
+        <v>0.2014598251552375</v>
       </c>
       <c r="T29">
-        <v>0.9404252509038113</v>
+        <v>0.9519961133794678</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.826725959486467</v>
+        <v>8.511485746647665</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3827,22 +3827,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.157784074111771</v>
+        <v>0.1576053412191116</v>
       </c>
       <c r="C30">
-        <v>342.8265162167933</v>
+        <v>339.8857212292817</v>
       </c>
       <c r="D30">
-        <v>441.7625162167932</v>
+        <v>442.4687212292817</v>
       </c>
       <c r="E30">
-        <v>-26.08399999999999</v>
+        <v>-22.43699999999998</v>
       </c>
       <c r="F30">
-        <v>102.116</v>
+        <v>105.763</v>
       </c>
       <c r="G30">
         <v>3.18</v>
@@ -3863,28 +3863,28 @@
         <v>46.5</v>
       </c>
       <c r="M30">
-        <v>5.463206</v>
+        <v>5.6583205</v>
       </c>
       <c r="N30">
-        <v>41.036794</v>
+        <v>40.8416795</v>
       </c>
       <c r="O30">
-        <v>6.1555191</v>
+        <v>6.126251924999999</v>
       </c>
       <c r="P30">
-        <v>34.8812749</v>
+        <v>34.715427575</v>
       </c>
       <c r="Q30">
-        <v>52.3812749</v>
+        <v>52.215427575</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2014598251552375</v>
+        <v>0.2034050580550868</v>
       </c>
       <c r="T30">
-        <v>0.9519961133794678</v>
+        <v>0.9638929156431706</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.511485746647665</v>
+        <v>8.217986238142572</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3909,22 +3909,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1576053412191116</v>
+        <v>0.1574266083264523</v>
       </c>
       <c r="C31">
-        <v>339.8857212292817</v>
+        <v>336.9471877467389</v>
       </c>
       <c r="D31">
-        <v>442.4687212292817</v>
+        <v>443.1771877467389</v>
       </c>
       <c r="E31">
-        <v>-22.437</v>
+        <v>-18.78999999999999</v>
       </c>
       <c r="F31">
-        <v>105.763</v>
+        <v>109.41</v>
       </c>
       <c r="G31">
         <v>3.18</v>
@@ -3945,28 +3945,28 @@
         <v>46.5</v>
       </c>
       <c r="M31">
-        <v>5.658320499999999</v>
+        <v>5.853434999999999</v>
       </c>
       <c r="N31">
-        <v>40.8416795</v>
+        <v>40.646565</v>
       </c>
       <c r="O31">
-        <v>6.126251924999999</v>
+        <v>6.09698475</v>
       </c>
       <c r="P31">
-        <v>34.715427575</v>
+        <v>34.54958025000001</v>
       </c>
       <c r="Q31">
-        <v>52.215427575</v>
+        <v>52.04958025000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2034050580550868</v>
+        <v>0.205405869037789</v>
       </c>
       <c r="T31">
-        <v>0.9638929156431706</v>
+        <v>0.9761296265429793</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.217986238142572</v>
+        <v>7.944053363537821</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3991,22 +3991,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1574266083264523</v>
+        <v>0.157247875433793</v>
       </c>
       <c r="C32">
-        <v>336.9471877467389</v>
+        <v>334.0109266497308</v>
       </c>
       <c r="D32">
-        <v>443.1771877467389</v>
+        <v>443.8879266497308</v>
       </c>
       <c r="E32">
-        <v>-18.78999999999999</v>
+        <v>-15.14299999999999</v>
       </c>
       <c r="F32">
-        <v>109.41</v>
+        <v>113.057</v>
       </c>
       <c r="G32">
         <v>3.18</v>
@@ -4027,28 +4027,28 @@
         <v>46.5</v>
       </c>
       <c r="M32">
-        <v>5.853434999999999</v>
+        <v>6.0485495</v>
       </c>
       <c r="N32">
-        <v>40.646565</v>
+        <v>40.4514505</v>
       </c>
       <c r="O32">
-        <v>6.09698475</v>
+        <v>6.067717575</v>
       </c>
       <c r="P32">
-        <v>34.54958025000001</v>
+        <v>34.383732925</v>
       </c>
       <c r="Q32">
-        <v>52.04958025000001</v>
+        <v>51.883732925</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.205405869037789</v>
+        <v>0.2074646745417289</v>
       </c>
       <c r="T32">
-        <v>0.9761296265429793</v>
+        <v>0.9887210247152464</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.944053363537821</v>
+        <v>7.687793577617245</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4073,22 +4073,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.157247875433793</v>
+        <v>0.1572867425411336</v>
       </c>
       <c r="C33">
-        <v>334.0109266497308</v>
+        <v>330.2091760551843</v>
       </c>
       <c r="D33">
-        <v>443.8879266497308</v>
+        <v>443.7331760551843</v>
       </c>
       <c r="E33">
-        <v>-15.14299999999999</v>
+        <v>-11.496</v>
       </c>
       <c r="F33">
-        <v>113.057</v>
+        <v>116.704</v>
       </c>
       <c r="G33">
         <v>3.18</v>
@@ -4109,45 +4109,45 @@
         <v>46.5</v>
       </c>
       <c r="M33">
-        <v>6.0485495</v>
+        <v>6.3370272</v>
       </c>
       <c r="N33">
-        <v>40.4514505</v>
+        <v>40.1629728</v>
       </c>
       <c r="O33">
-        <v>6.067717575</v>
+        <v>6.02444592</v>
       </c>
       <c r="P33">
-        <v>34.383732925</v>
+        <v>34.13852688</v>
       </c>
       <c r="Q33">
-        <v>51.883732925</v>
+        <v>51.63852688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2074646745417289</v>
+        <v>0.2095840331487259</v>
       </c>
       <c r="T33">
-        <v>0.9887210247152464</v>
+        <v>1.001682758127874</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.687793577617245</v>
+        <v>7.33782553434519</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4155,22 +4155,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1572867425411336</v>
+        <v>0.1571148096484742</v>
       </c>
       <c r="C34">
-        <v>330.2091760551843</v>
+        <v>327.2475505239454</v>
       </c>
       <c r="D34">
-        <v>443.7331760551843</v>
+        <v>444.4185505239454</v>
       </c>
       <c r="E34">
-        <v>-11.496</v>
+        <v>-7.84899999999999</v>
       </c>
       <c r="F34">
-        <v>116.704</v>
+        <v>120.351</v>
       </c>
       <c r="G34">
         <v>3.18</v>
@@ -4191,28 +4191,28 @@
         <v>46.5</v>
       </c>
       <c r="M34">
-        <v>6.3370272</v>
+        <v>6.5350593</v>
       </c>
       <c r="N34">
-        <v>40.1629728</v>
+        <v>39.9649407</v>
       </c>
       <c r="O34">
-        <v>6.02444592</v>
+        <v>5.994741105</v>
       </c>
       <c r="P34">
-        <v>34.13852688</v>
+        <v>33.970199595</v>
       </c>
       <c r="Q34">
-        <v>51.63852688</v>
+        <v>51.470199595</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2095840331487259</v>
+        <v>0.2117666561917526</v>
       </c>
       <c r="T34">
-        <v>1.001682758127874</v>
+        <v>1.015031408955804</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.33782553434519</v>
+        <v>7.115467184819577</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4237,22 +4237,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1571148096484742</v>
+        <v>0.1569428767558149</v>
       </c>
       <c r="C35">
-        <v>327.2475505239454</v>
+        <v>324.288045477949</v>
       </c>
       <c r="D35">
-        <v>444.4185505239454</v>
+        <v>445.106045477949</v>
       </c>
       <c r="E35">
-        <v>-7.84899999999999</v>
+        <v>-4.201999999999984</v>
       </c>
       <c r="F35">
-        <v>120.351</v>
+        <v>123.998</v>
       </c>
       <c r="G35">
         <v>3.18</v>
@@ -4273,28 +4273,28 @@
         <v>46.5</v>
       </c>
       <c r="M35">
-        <v>6.5350593</v>
+        <v>6.7330914</v>
       </c>
       <c r="N35">
-        <v>39.9649407</v>
+        <v>39.7669086</v>
       </c>
       <c r="O35">
-        <v>5.994741105</v>
+        <v>5.96503629</v>
       </c>
       <c r="P35">
-        <v>33.970199595</v>
+        <v>33.80187231</v>
       </c>
       <c r="Q35">
-        <v>51.470199595</v>
+        <v>51.30187231</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2117666561917526</v>
+        <v>0.2140154193269923</v>
       </c>
       <c r="T35">
-        <v>1.015031408955804</v>
+        <v>1.028784564354278</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.115467184819577</v>
+        <v>6.906188738207237</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4319,22 +4319,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1569428767558149</v>
+        <v>0.1567709438631556</v>
       </c>
       <c r="C36">
-        <v>324.288045477949</v>
+        <v>321.3306707733194</v>
       </c>
       <c r="D36">
-        <v>445.106045477949</v>
+        <v>445.7956707733194</v>
       </c>
       <c r="E36">
-        <v>-4.201999999999984</v>
+        <v>-0.5549999999999784</v>
       </c>
       <c r="F36">
-        <v>123.998</v>
+        <v>127.645</v>
       </c>
       <c r="G36">
         <v>3.18</v>
@@ -4355,28 +4355,28 @@
         <v>46.5</v>
       </c>
       <c r="M36">
-        <v>6.7330914</v>
+        <v>6.931123500000001</v>
       </c>
       <c r="N36">
-        <v>39.7669086</v>
+        <v>39.5688765</v>
       </c>
       <c r="O36">
-        <v>5.96503629</v>
+        <v>5.935331475</v>
       </c>
       <c r="P36">
-        <v>33.80187231</v>
+        <v>33.633545025</v>
       </c>
       <c r="Q36">
-        <v>51.30187231</v>
+        <v>51.133545025</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2140154193269923</v>
+        <v>0.2163333751740855</v>
       </c>
       <c r="T36">
-        <v>1.028784564354278</v>
+        <v>1.042960893765012</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.906188738207237</v>
+        <v>6.708869059972744</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4401,22 +4401,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1567709438631556</v>
+        <v>0.1565990109704962</v>
       </c>
       <c r="C37">
-        <v>321.3306707733194</v>
+        <v>318.3754363273595</v>
       </c>
       <c r="D37">
-        <v>445.7956707733194</v>
+        <v>446.4874363273594</v>
       </c>
       <c r="E37">
-        <v>-0.5549999999999784</v>
+        <v>3.092000000000013</v>
       </c>
       <c r="F37">
-        <v>127.645</v>
+        <v>131.292</v>
       </c>
       <c r="G37">
         <v>3.18</v>
@@ -4437,28 +4437,28 @@
         <v>46.5</v>
       </c>
       <c r="M37">
-        <v>6.931123500000001</v>
+        <v>7.1291556</v>
       </c>
       <c r="N37">
-        <v>39.5688765</v>
+        <v>39.3708444</v>
       </c>
       <c r="O37">
-        <v>5.935331475</v>
+        <v>5.90562666</v>
       </c>
       <c r="P37">
-        <v>33.633545025</v>
+        <v>33.46521774</v>
       </c>
       <c r="Q37">
-        <v>51.133545025</v>
+        <v>50.96521774</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2163333751740855</v>
+        <v>0.2187237671414003</v>
       </c>
       <c r="T37">
-        <v>1.042960893765012</v>
+        <v>1.057580233469831</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.708869059972744</v>
+        <v>6.522511586084613</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4483,22 +4483,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1565990109704962</v>
+        <v>0.1564270780778368</v>
       </c>
       <c r="C38">
-        <v>318.3754363273596</v>
+        <v>315.4223521190231</v>
       </c>
       <c r="D38">
-        <v>446.4874363273596</v>
+        <v>447.1813521190231</v>
       </c>
       <c r="E38">
-        <v>3.092000000000013</v>
+        <v>6.739000000000004</v>
       </c>
       <c r="F38">
-        <v>131.292</v>
+        <v>134.939</v>
       </c>
       <c r="G38">
         <v>3.18</v>
@@ -4519,28 +4519,28 @@
         <v>46.5</v>
       </c>
       <c r="M38">
-        <v>7.1291556</v>
+        <v>7.3271877</v>
       </c>
       <c r="N38">
-        <v>39.3708444</v>
+        <v>39.1728123</v>
       </c>
       <c r="O38">
-        <v>5.90562666</v>
+        <v>5.875921845000001</v>
       </c>
       <c r="P38">
-        <v>33.46521774</v>
+        <v>33.296890455</v>
       </c>
       <c r="Q38">
-        <v>50.96521774</v>
+        <v>50.796890455</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2187237671414003</v>
+        <v>0.221190044567995</v>
       </c>
       <c r="T38">
-        <v>1.057580233469831</v>
+        <v>1.072663679197026</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.522511586084613</v>
+        <v>6.346227489163408</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4565,22 +4565,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1564270780778368</v>
+        <v>0.1562551451851775</v>
       </c>
       <c r="C39">
-        <v>315.4223521190231</v>
+        <v>312.4714281893977</v>
       </c>
       <c r="D39">
-        <v>447.1813521190231</v>
+        <v>447.8774281893976</v>
       </c>
       <c r="E39">
-        <v>6.739000000000004</v>
+        <v>10.386</v>
       </c>
       <c r="F39">
-        <v>134.939</v>
+        <v>138.586</v>
       </c>
       <c r="G39">
         <v>3.18</v>
@@ -4601,28 +4601,28 @@
         <v>46.5</v>
       </c>
       <c r="M39">
-        <v>7.3271877</v>
+        <v>7.525219799999999</v>
       </c>
       <c r="N39">
-        <v>39.1728123</v>
+        <v>38.9747802</v>
       </c>
       <c r="O39">
-        <v>5.875921845000001</v>
+        <v>5.846217029999999</v>
       </c>
       <c r="P39">
-        <v>33.296890455</v>
+        <v>33.12856317</v>
       </c>
       <c r="Q39">
-        <v>50.796890455</v>
+        <v>50.62856317</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.221190044567995</v>
+        <v>0.2237358793309315</v>
       </c>
       <c r="T39">
-        <v>1.072663679197026</v>
+        <v>1.088233687689614</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.346227489163408</v>
+        <v>6.179221502606476</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4647,22 +4647,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1562551451851775</v>
+        <v>0.1564147122925181</v>
       </c>
       <c r="C40">
-        <v>312.4714281893977</v>
+        <v>308.1783431960167</v>
       </c>
       <c r="D40">
-        <v>447.8774281893976</v>
+        <v>447.2313431960167</v>
       </c>
       <c r="E40">
-        <v>10.386</v>
+        <v>14.03300000000002</v>
       </c>
       <c r="F40">
-        <v>138.586</v>
+        <v>142.233</v>
       </c>
       <c r="G40">
         <v>3.18</v>
@@ -4683,45 +4683,45 @@
         <v>46.5</v>
       </c>
       <c r="M40">
-        <v>7.525219799999999</v>
+        <v>7.8654849</v>
       </c>
       <c r="N40">
-        <v>38.9747802</v>
+        <v>38.6345151</v>
       </c>
       <c r="O40">
-        <v>5.846217029999999</v>
+        <v>5.795177265</v>
       </c>
       <c r="P40">
-        <v>33.12856317</v>
+        <v>32.839337835</v>
       </c>
       <c r="Q40">
-        <v>50.62856317</v>
+        <v>50.339337835</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2237358793309315</v>
+        <v>0.2263651840860953</v>
       </c>
       <c r="T40">
-        <v>1.088233687689614</v>
+        <v>1.104314188263927</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.179221502606476</v>
+        <v>5.911905062585525</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4729,22 +4729,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1564147122925181</v>
+        <v>0.1562512793998588</v>
       </c>
       <c r="C41">
-        <v>308.1783431960167</v>
+        <v>305.193103861023</v>
       </c>
       <c r="D41">
-        <v>447.2313431960167</v>
+        <v>447.893103861023</v>
       </c>
       <c r="E41">
-        <v>14.03300000000002</v>
+        <v>17.68000000000001</v>
       </c>
       <c r="F41">
-        <v>142.233</v>
+        <v>145.88</v>
       </c>
       <c r="G41">
         <v>3.18</v>
@@ -4765,28 +4765,28 @@
         <v>46.5</v>
       </c>
       <c r="M41">
-        <v>7.8654849</v>
+        <v>8.067164</v>
       </c>
       <c r="N41">
-        <v>38.6345151</v>
+        <v>38.432836</v>
       </c>
       <c r="O41">
-        <v>5.795177265</v>
+        <v>5.7649254</v>
       </c>
       <c r="P41">
-        <v>32.839337835</v>
+        <v>32.6679106</v>
       </c>
       <c r="Q41">
-        <v>50.339337835</v>
+        <v>50.1679106</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2263651840860953</v>
+        <v>0.229082132333098</v>
       </c>
       <c r="T41">
-        <v>1.104314188263927</v>
+        <v>1.12093070552405</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.911905062585525</v>
+        <v>5.764107436020887</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1562512793998588</v>
+        <v>0.1560878465071995</v>
       </c>
       <c r="C42">
-        <v>305.193103861023</v>
+        <v>302.2098258202816</v>
       </c>
       <c r="D42">
-        <v>447.893103861023</v>
+        <v>448.5568258202816</v>
       </c>
       <c r="E42">
-        <v>17.68000000000001</v>
+        <v>21.32700000000003</v>
       </c>
       <c r="F42">
-        <v>145.88</v>
+        <v>149.527</v>
       </c>
       <c r="G42">
         <v>3.18</v>
@@ -4847,28 +4847,28 @@
         <v>46.5</v>
       </c>
       <c r="M42">
-        <v>8.067164</v>
+        <v>8.268843100000002</v>
       </c>
       <c r="N42">
-        <v>38.432836</v>
+        <v>38.2311569</v>
       </c>
       <c r="O42">
-        <v>5.7649254</v>
+        <v>5.734673535</v>
       </c>
       <c r="P42">
-        <v>32.6679106</v>
+        <v>32.496483365</v>
       </c>
       <c r="Q42">
-        <v>50.1679106</v>
+        <v>49.996483365</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.229082132333098</v>
+        <v>0.231891180520677</v>
       </c>
       <c r="T42">
-        <v>1.12093070552405</v>
+        <v>1.138110494555702</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.764107436020887</v>
+        <v>5.623519449776474</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4893,22 +4893,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1560878465071995</v>
+        <v>0.1559244136145401</v>
       </c>
       <c r="C43">
-        <v>302.2098258202816</v>
+        <v>299.2285178059161</v>
       </c>
       <c r="D43">
-        <v>448.5568258202816</v>
+        <v>449.2225178059161</v>
       </c>
       <c r="E43">
-        <v>21.32700000000003</v>
+        <v>24.97400000000002</v>
       </c>
       <c r="F43">
-        <v>149.527</v>
+        <v>153.174</v>
       </c>
       <c r="G43">
         <v>3.18</v>
@@ -4929,28 +4929,28 @@
         <v>46.5</v>
       </c>
       <c r="M43">
-        <v>8.268843100000002</v>
+        <v>8.470522200000001</v>
       </c>
       <c r="N43">
-        <v>38.2311569</v>
+        <v>38.0294778</v>
       </c>
       <c r="O43">
-        <v>5.734673535</v>
+        <v>5.704421669999999</v>
       </c>
       <c r="P43">
-        <v>32.496483365</v>
+        <v>32.32505612999999</v>
       </c>
       <c r="Q43">
-        <v>49.996483365</v>
+        <v>49.82505612999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.231891180520677</v>
+        <v>0.2347970924388623</v>
       </c>
       <c r="T43">
-        <v>1.138110494555702</v>
+        <v>1.155882690105687</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.623519449776474</v>
+        <v>5.489626129543701</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4975,22 +4975,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1559244136145401</v>
+        <v>0.1557609807218808</v>
       </c>
       <c r="C44">
-        <v>299.2285178059161</v>
+        <v>296.2491886019636</v>
       </c>
       <c r="D44">
-        <v>449.2225178059161</v>
+        <v>449.8901886019636</v>
       </c>
       <c r="E44">
-        <v>24.97399999999999</v>
+        <v>28.62100000000001</v>
       </c>
       <c r="F44">
-        <v>153.174</v>
+        <v>156.821</v>
       </c>
       <c r="G44">
         <v>3.18</v>
@@ -5011,28 +5011,28 @@
         <v>46.5</v>
       </c>
       <c r="M44">
-        <v>8.4705222</v>
+        <v>8.672201299999999</v>
       </c>
       <c r="N44">
-        <v>38.0294778</v>
+        <v>37.8277987</v>
       </c>
       <c r="O44">
-        <v>5.70442167</v>
+        <v>5.674169805</v>
       </c>
       <c r="P44">
-        <v>32.32505613</v>
+        <v>32.153628895</v>
       </c>
       <c r="Q44">
-        <v>49.82505613</v>
+        <v>49.653628895</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2347970924388622</v>
+        <v>0.2378049661787382</v>
       </c>
       <c r="T44">
-        <v>1.155882690105687</v>
+        <v>1.174278471464444</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.489626129543702</v>
+        <v>5.361960405600826</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5057,22 +5057,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1557609807218808</v>
+        <v>0.1555975478292214</v>
       </c>
       <c r="C45">
-        <v>296.2491886019636</v>
+        <v>293.2718470447609</v>
       </c>
       <c r="D45">
-        <v>449.8901886019636</v>
+        <v>450.5598470447609</v>
       </c>
       <c r="E45">
-        <v>28.62100000000001</v>
+        <v>32.268</v>
       </c>
       <c r="F45">
-        <v>156.821</v>
+        <v>160.468</v>
       </c>
       <c r="G45">
         <v>3.18</v>
@@ -5093,28 +5093,28 @@
         <v>46.5</v>
       </c>
       <c r="M45">
-        <v>8.672201299999999</v>
+        <v>8.873880399999999</v>
       </c>
       <c r="N45">
-        <v>37.8277987</v>
+        <v>37.6261196</v>
       </c>
       <c r="O45">
-        <v>5.674169805</v>
+        <v>5.643917940000001</v>
       </c>
       <c r="P45">
-        <v>32.153628895</v>
+        <v>31.98220166</v>
       </c>
       <c r="Q45">
-        <v>49.653628895</v>
+        <v>49.48220166</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2378049661787382</v>
+        <v>0.2409202639807525</v>
       </c>
       <c r="T45">
-        <v>1.174278471464444</v>
+        <v>1.193331245014585</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.361960405600826</v>
+        <v>5.240097669109898</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5139,22 +5139,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1555975478292214</v>
+        <v>0.1554341149365621</v>
       </c>
       <c r="C46">
-        <v>293.2718470447609</v>
+        <v>290.2965020233348</v>
       </c>
       <c r="D46">
-        <v>450.5598470447609</v>
+        <v>451.2315020233348</v>
       </c>
       <c r="E46">
-        <v>32.268</v>
+        <v>35.91500000000002</v>
       </c>
       <c r="F46">
-        <v>160.468</v>
+        <v>164.115</v>
       </c>
       <c r="G46">
         <v>3.18</v>
@@ -5175,28 +5175,28 @@
         <v>46.5</v>
       </c>
       <c r="M46">
-        <v>8.873880399999999</v>
+        <v>9.075559500000001</v>
       </c>
       <c r="N46">
-        <v>37.6261196</v>
+        <v>37.4244405</v>
       </c>
       <c r="O46">
-        <v>5.643917940000001</v>
+        <v>5.613666075</v>
       </c>
       <c r="P46">
-        <v>31.98220166</v>
+        <v>31.810774425</v>
       </c>
       <c r="Q46">
-        <v>49.48220166</v>
+        <v>49.31077442500001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2409202639807525</v>
+        <v>0.2441488453392037</v>
       </c>
       <c r="T46">
-        <v>1.193331245014585</v>
+        <v>1.213076846693821</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.240097669109898</v>
+        <v>5.123651054240788</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5221,22 +5221,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1554341149365621</v>
+        <v>0.1552706820439027</v>
       </c>
       <c r="C47">
-        <v>290.2965020233348</v>
+        <v>287.3231624797947</v>
       </c>
       <c r="D47">
-        <v>451.2315020233348</v>
+        <v>451.9051624797947</v>
       </c>
       <c r="E47">
-        <v>35.91500000000002</v>
+        <v>39.56200000000001</v>
       </c>
       <c r="F47">
-        <v>164.115</v>
+        <v>167.762</v>
       </c>
       <c r="G47">
         <v>3.18</v>
@@ -5257,28 +5257,28 @@
         <v>46.5</v>
       </c>
       <c r="M47">
-        <v>9.075559500000001</v>
+        <v>9.2772386</v>
       </c>
       <c r="N47">
-        <v>37.4244405</v>
+        <v>37.2227614</v>
       </c>
       <c r="O47">
-        <v>5.613666075</v>
+        <v>5.583414209999999</v>
       </c>
       <c r="P47">
-        <v>31.810774425</v>
+        <v>31.63934719</v>
       </c>
       <c r="Q47">
-        <v>49.31077442500001</v>
+        <v>49.13934719</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2441488453392037</v>
+        <v>0.247497003785005</v>
       </c>
       <c r="T47">
-        <v>1.213076846693821</v>
+        <v>1.233553766953771</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.123651054240788</v>
+        <v>5.012267335670336</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5303,22 +5303,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1552706820439027</v>
+        <v>0.1551072491512434</v>
       </c>
       <c r="C48">
-        <v>287.3231624797947</v>
+        <v>284.3518374097309</v>
       </c>
       <c r="D48">
-        <v>451.9051624797947</v>
+        <v>452.5808374097309</v>
       </c>
       <c r="E48">
-        <v>39.56200000000001</v>
+        <v>43.209</v>
       </c>
       <c r="F48">
-        <v>167.762</v>
+        <v>171.409</v>
       </c>
       <c r="G48">
         <v>3.18</v>
@@ -5339,28 +5339,28 @@
         <v>46.5</v>
       </c>
       <c r="M48">
-        <v>9.2772386</v>
+        <v>9.4789177</v>
       </c>
       <c r="N48">
-        <v>37.2227614</v>
+        <v>37.0210823</v>
       </c>
       <c r="O48">
-        <v>5.583414209999999</v>
+        <v>5.553162345</v>
       </c>
       <c r="P48">
-        <v>31.63934719</v>
+        <v>31.467919955</v>
       </c>
       <c r="Q48">
-        <v>49.13934719</v>
+        <v>48.967919955</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.247497003785005</v>
+        <v>0.2509715078325346</v>
       </c>
       <c r="T48">
-        <v>1.233553766953771</v>
+        <v>1.254803401185794</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.012267335670336</v>
+        <v>4.90562334980501</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5385,22 +5385,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1551072491512434</v>
+        <v>0.154943816258584</v>
       </c>
       <c r="C49">
-        <v>284.3518374097309</v>
+        <v>281.3825358626128</v>
       </c>
       <c r="D49">
-        <v>452.5808374097309</v>
+        <v>453.2585358626128</v>
       </c>
       <c r="E49">
-        <v>43.209</v>
+        <v>46.85600000000002</v>
       </c>
       <c r="F49">
-        <v>171.409</v>
+        <v>175.056</v>
       </c>
       <c r="G49">
         <v>3.18</v>
@@ -5421,28 +5421,28 @@
         <v>46.5</v>
       </c>
       <c r="M49">
-        <v>9.4789177</v>
+        <v>9.680596800000002</v>
       </c>
       <c r="N49">
-        <v>37.0210823</v>
+        <v>36.8194032</v>
       </c>
       <c r="O49">
-        <v>5.553162345</v>
+        <v>5.522910479999999</v>
       </c>
       <c r="P49">
-        <v>31.467919955</v>
+        <v>31.29649272</v>
       </c>
       <c r="Q49">
-        <v>48.967919955</v>
+        <v>48.79649272</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2509715078325346</v>
+        <v>0.254579646651123</v>
       </c>
       <c r="T49">
-        <v>1.254803401185794</v>
+        <v>1.276870329042125</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.90562334980501</v>
+        <v>4.803422863350738</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5467,22 +5467,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.154943816258584</v>
+        <v>0.1547803833659247</v>
       </c>
       <c r="C50">
-        <v>281.3825358626128</v>
+        <v>278.4152669421945</v>
       </c>
       <c r="D50">
-        <v>453.2585358626128</v>
+        <v>453.9382669421946</v>
       </c>
       <c r="E50">
-        <v>46.85599999999999</v>
+        <v>50.50300000000001</v>
       </c>
       <c r="F50">
-        <v>175.056</v>
+        <v>178.703</v>
       </c>
       <c r="G50">
         <v>3.18</v>
@@ -5503,28 +5503,28 @@
         <v>46.5</v>
       </c>
       <c r="M50">
-        <v>9.6805968</v>
+        <v>9.8822759</v>
       </c>
       <c r="N50">
-        <v>36.8194032</v>
+        <v>36.6177241</v>
       </c>
       <c r="O50">
-        <v>5.522910479999999</v>
+        <v>5.492658615000001</v>
       </c>
       <c r="P50">
-        <v>31.29649272</v>
+        <v>31.125065485</v>
       </c>
       <c r="Q50">
-        <v>48.79649272</v>
+        <v>48.62506548500001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.254579646651123</v>
+        <v>0.2583292811096562</v>
       </c>
       <c r="T50">
-        <v>1.276870329042125</v>
+        <v>1.299802626618313</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.803422863350738</v>
+        <v>4.705393825323173</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5549,22 +5549,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1547803833659247</v>
+        <v>0.1546169504732653</v>
       </c>
       <c r="C51">
-        <v>278.4152669421945</v>
+        <v>275.4500398069227</v>
       </c>
       <c r="D51">
-        <v>453.9382669421946</v>
+        <v>454.6200398069228</v>
       </c>
       <c r="E51">
-        <v>50.50300000000001</v>
+        <v>54.15000000000001</v>
       </c>
       <c r="F51">
-        <v>178.703</v>
+        <v>182.35</v>
       </c>
       <c r="G51">
         <v>3.18</v>
@@ -5585,28 +5585,28 @@
         <v>46.5</v>
       </c>
       <c r="M51">
-        <v>9.8822759</v>
+        <v>10.083955</v>
       </c>
       <c r="N51">
-        <v>36.6177241</v>
+        <v>36.416045</v>
       </c>
       <c r="O51">
-        <v>5.492658615000001</v>
+        <v>5.46240675</v>
       </c>
       <c r="P51">
-        <v>31.125065485</v>
+        <v>30.95363825</v>
       </c>
       <c r="Q51">
-        <v>48.62506548500001</v>
+        <v>48.45363825</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2583292811096562</v>
+        <v>0.2622289009465306</v>
       </c>
       <c r="T51">
-        <v>1.299802626618313</v>
+        <v>1.323652216097548</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.705393825323173</v>
+        <v>4.611285948816709</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1546169504732653</v>
+        <v>0.154453517580606</v>
       </c>
       <c r="C52">
-        <v>275.4500398069227</v>
+        <v>272.4868636703465</v>
       </c>
       <c r="D52">
-        <v>454.6200398069228</v>
+        <v>455.3038636703465</v>
       </c>
       <c r="E52">
-        <v>54.15000000000001</v>
+        <v>57.797</v>
       </c>
       <c r="F52">
-        <v>182.35</v>
+        <v>185.997</v>
       </c>
       <c r="G52">
         <v>3.18</v>
@@ -5667,28 +5667,28 @@
         <v>46.5</v>
       </c>
       <c r="M52">
-        <v>10.083955</v>
+        <v>10.2856341</v>
       </c>
       <c r="N52">
-        <v>36.416045</v>
+        <v>36.2143659</v>
       </c>
       <c r="O52">
-        <v>5.46240675</v>
+        <v>5.432154885</v>
       </c>
       <c r="P52">
-        <v>30.95363825</v>
+        <v>30.78221101500001</v>
       </c>
       <c r="Q52">
-        <v>48.45363825</v>
+        <v>48.282211015</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2622289009465306</v>
+        <v>0.2662876889400122</v>
       </c>
       <c r="T52">
-        <v>1.323652216097548</v>
+        <v>1.348475258208589</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.611285948816709</v>
+        <v>4.520868577271284</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5713,22 +5713,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.154453517580606</v>
+        <v>0.1553950846879466</v>
       </c>
       <c r="C53">
-        <v>272.4868636703465</v>
+        <v>264.9281997202912</v>
       </c>
       <c r="D53">
-        <v>455.3038636703465</v>
+        <v>451.3921997202912</v>
       </c>
       <c r="E53">
-        <v>57.797</v>
+        <v>61.44400000000002</v>
       </c>
       <c r="F53">
-        <v>185.997</v>
+        <v>189.644</v>
       </c>
       <c r="G53">
         <v>3.18</v>
@@ -5749,45 +5749,45 @@
         <v>46.5</v>
       </c>
       <c r="M53">
-        <v>10.2856341</v>
+        <v>10.9614232</v>
       </c>
       <c r="N53">
-        <v>36.2143659</v>
+        <v>35.5385768</v>
       </c>
       <c r="O53">
-        <v>5.432154885</v>
+        <v>5.33078652</v>
       </c>
       <c r="P53">
-        <v>30.78221101500001</v>
+        <v>30.20779028</v>
       </c>
       <c r="Q53">
-        <v>48.282211015</v>
+        <v>47.70779028</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2662876889400122</v>
+        <v>0.2705155930998888</v>
       </c>
       <c r="T53">
-        <v>1.348475258208589</v>
+        <v>1.374332593740923</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.520868577271284</v>
+        <v>4.242149869735893</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1553950846879466</v>
+        <v>0.1552529017952873</v>
       </c>
       <c r="C54">
-        <v>264.9281997202912</v>
+        <v>261.8675729239924</v>
       </c>
       <c r="D54">
-        <v>451.3921997202912</v>
+        <v>451.9785729239924</v>
       </c>
       <c r="E54">
-        <v>61.44400000000002</v>
+        <v>65.09100000000001</v>
       </c>
       <c r="F54">
-        <v>189.644</v>
+        <v>193.291</v>
       </c>
       <c r="G54">
         <v>3.18</v>
@@ -5831,28 +5831,28 @@
         <v>46.5</v>
       </c>
       <c r="M54">
-        <v>10.9614232</v>
+        <v>11.1722198</v>
       </c>
       <c r="N54">
-        <v>35.5385768</v>
+        <v>35.3277802</v>
       </c>
       <c r="O54">
-        <v>5.33078652</v>
+        <v>5.29916703</v>
       </c>
       <c r="P54">
-        <v>30.20779028</v>
+        <v>30.02861317</v>
       </c>
       <c r="Q54">
-        <v>47.70779028</v>
+        <v>47.52861317</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2705155930998888</v>
+        <v>0.2749234080750793</v>
       </c>
       <c r="T54">
-        <v>1.374332593740923</v>
+        <v>1.401290241423568</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.242149869735893</v>
+        <v>4.162109306155971</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1552529017952873</v>
+        <v>0.1551107189026279</v>
       </c>
       <c r="C55">
-        <v>261.8675729239924</v>
+        <v>258.8084715451297</v>
       </c>
       <c r="D55">
-        <v>451.9785729239924</v>
+        <v>452.5664715451297</v>
       </c>
       <c r="E55">
-        <v>65.09100000000001</v>
+        <v>68.73800000000003</v>
       </c>
       <c r="F55">
-        <v>193.291</v>
+        <v>196.938</v>
       </c>
       <c r="G55">
         <v>3.18</v>
@@ -5913,28 +5913,28 @@
         <v>46.5</v>
       </c>
       <c r="M55">
-        <v>11.1722198</v>
+        <v>11.3830164</v>
       </c>
       <c r="N55">
-        <v>35.3277802</v>
+        <v>35.1169836</v>
       </c>
       <c r="O55">
-        <v>5.29916703</v>
+        <v>5.26754754</v>
       </c>
       <c r="P55">
-        <v>30.02861317</v>
+        <v>29.84943606</v>
       </c>
       <c r="Q55">
-        <v>47.52861317</v>
+        <v>47.34943606</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2749234080750793</v>
+        <v>0.2795228671796259</v>
       </c>
       <c r="T55">
-        <v>1.401290241423568</v>
+        <v>1.429419960744591</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.162109306155971</v>
+        <v>4.085033207893822</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5959,22 +5959,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1551107189026279</v>
+        <v>0.1549685360099686</v>
       </c>
       <c r="C56">
-        <v>258.8084715451297</v>
+        <v>255.7509015438889</v>
       </c>
       <c r="D56">
-        <v>452.5664715451297</v>
+        <v>453.1559015438889</v>
       </c>
       <c r="E56">
-        <v>68.73800000000003</v>
+        <v>72.38500000000002</v>
       </c>
       <c r="F56">
-        <v>196.938</v>
+        <v>200.585</v>
       </c>
       <c r="G56">
         <v>3.18</v>
@@ -5995,28 +5995,28 @@
         <v>46.5</v>
       </c>
       <c r="M56">
-        <v>11.3830164</v>
+        <v>11.593813</v>
       </c>
       <c r="N56">
-        <v>35.1169836</v>
+        <v>34.906187</v>
       </c>
       <c r="O56">
-        <v>5.26754754</v>
+        <v>5.23592805</v>
       </c>
       <c r="P56">
-        <v>29.84943606</v>
+        <v>29.67025895</v>
       </c>
       <c r="Q56">
-        <v>47.34943606</v>
+        <v>47.17025895</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2795228671796259</v>
+        <v>0.2843267466888191</v>
       </c>
       <c r="T56">
-        <v>1.429419960744591</v>
+        <v>1.458799889813214</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.085033207893822</v>
+        <v>4.010759876841208</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6041,22 +6041,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1549685360099686</v>
+        <v>0.1564923531173092</v>
       </c>
       <c r="C57">
-        <v>255.7509015438889</v>
+        <v>245.8656502499344</v>
       </c>
       <c r="D57">
-        <v>453.1559015438889</v>
+        <v>446.9176502499344</v>
       </c>
       <c r="E57">
-        <v>72.38500000000002</v>
+        <v>76.03200000000001</v>
       </c>
       <c r="F57">
-        <v>200.585</v>
+        <v>204.232</v>
       </c>
       <c r="G57">
         <v>3.18</v>
@@ -6077,45 +6077,45 @@
         <v>46.5</v>
       </c>
       <c r="M57">
-        <v>11.593813</v>
+        <v>12.5194216</v>
       </c>
       <c r="N57">
-        <v>34.906187</v>
+        <v>33.9805784</v>
       </c>
       <c r="O57">
-        <v>5.23592805</v>
+        <v>5.09708676</v>
       </c>
       <c r="P57">
-        <v>29.67025895</v>
+        <v>28.88349164</v>
       </c>
       <c r="Q57">
-        <v>47.17025895</v>
+        <v>46.38349164</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2843267466888191</v>
+        <v>0.2893489843575209</v>
       </c>
       <c r="T57">
-        <v>1.458799889813214</v>
+        <v>1.489515270203138</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.15</v>
       </c>
       <c r="W57">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.010759876841208</v>
+        <v>3.714229098251632</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6123,22 +6123,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1564923531173092</v>
+        <v>0.1563799202246499</v>
       </c>
       <c r="C58">
-        <v>245.8656502499344</v>
+        <v>242.6730568374597</v>
       </c>
       <c r="D58">
-        <v>446.9176502499344</v>
+        <v>447.3720568374597</v>
       </c>
       <c r="E58">
-        <v>76.03200000000001</v>
+        <v>79.67900000000003</v>
       </c>
       <c r="F58">
-        <v>204.232</v>
+        <v>207.879</v>
       </c>
       <c r="G58">
         <v>3.18</v>
@@ -6159,28 +6159,28 @@
         <v>46.5</v>
       </c>
       <c r="M58">
-        <v>12.5194216</v>
+        <v>12.7429827</v>
       </c>
       <c r="N58">
-        <v>33.9805784</v>
+        <v>33.7570173</v>
       </c>
       <c r="O58">
-        <v>5.09708676</v>
+        <v>5.063552595</v>
       </c>
       <c r="P58">
-        <v>28.88349164</v>
+        <v>28.693464705</v>
       </c>
       <c r="Q58">
-        <v>46.38349164</v>
+        <v>46.193464705</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2893489843575209</v>
+        <v>0.29460481447593</v>
       </c>
       <c r="T58">
-        <v>1.489515270203138</v>
+        <v>1.521659272936779</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.714229098251632</v>
+        <v>3.649067184247217</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6205,22 +6205,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1563799202246499</v>
+        <v>0.1562674873319905</v>
       </c>
       <c r="C59">
-        <v>242.6730568374597</v>
+        <v>239.4813884074993</v>
       </c>
       <c r="D59">
-        <v>447.3720568374597</v>
+        <v>447.8273884074993</v>
       </c>
       <c r="E59">
-        <v>79.67900000000003</v>
+        <v>83.32600000000002</v>
       </c>
       <c r="F59">
-        <v>207.879</v>
+        <v>211.526</v>
       </c>
       <c r="G59">
         <v>3.18</v>
@@ -6241,28 +6241,28 @@
         <v>46.5</v>
       </c>
       <c r="M59">
-        <v>12.7429827</v>
+        <v>12.9665438</v>
       </c>
       <c r="N59">
-        <v>33.7570173</v>
+        <v>33.5334562</v>
       </c>
       <c r="O59">
-        <v>5.063552595</v>
+        <v>5.03001843</v>
       </c>
       <c r="P59">
-        <v>28.693464705</v>
+        <v>28.50343777000001</v>
       </c>
       <c r="Q59">
-        <v>46.193464705</v>
+        <v>46.00343777000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.29460481447593</v>
+        <v>0.3001109222190251</v>
       </c>
       <c r="T59">
-        <v>1.521659272936779</v>
+        <v>1.555333942467261</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.649067184247217</v>
+        <v>3.586152232794679</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6287,22 +6287,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1562674873319905</v>
+        <v>0.1561550544393311</v>
       </c>
       <c r="C60">
-        <v>239.4813884074992</v>
+        <v>236.2906477872491</v>
       </c>
       <c r="D60">
-        <v>447.8273884074992</v>
+        <v>448.2836477872491</v>
       </c>
       <c r="E60">
-        <v>83.32599999999999</v>
+        <v>86.97299999999998</v>
       </c>
       <c r="F60">
-        <v>211.526</v>
+        <v>215.173</v>
       </c>
       <c r="G60">
         <v>3.18</v>
@@ -6323,28 +6323,28 @@
         <v>46.5</v>
       </c>
       <c r="M60">
-        <v>12.9665438</v>
+        <v>13.1901049</v>
       </c>
       <c r="N60">
-        <v>33.5334562</v>
+        <v>33.30989510000001</v>
       </c>
       <c r="O60">
-        <v>5.03001843</v>
+        <v>4.996484265</v>
       </c>
       <c r="P60">
-        <v>28.50343777000001</v>
+        <v>28.31341083500001</v>
       </c>
       <c r="Q60">
-        <v>46.00343777000001</v>
+        <v>45.81341083500001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.300110922219025</v>
+        <v>0.3058856205837345</v>
       </c>
       <c r="T60">
-        <v>1.55533394246726</v>
+        <v>1.590651278804106</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.586152232794679</v>
+        <v>3.525369991560872</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6369,22 +6369,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1561550544393311</v>
+        <v>0.1574706215466718</v>
       </c>
       <c r="C61">
-        <v>236.2906477872491</v>
+        <v>227.3625164241438</v>
       </c>
       <c r="D61">
-        <v>448.2836477872491</v>
+        <v>443.0025164241438</v>
       </c>
       <c r="E61">
-        <v>86.97299999999998</v>
+        <v>90.62</v>
       </c>
       <c r="F61">
-        <v>215.173</v>
+        <v>218.82</v>
       </c>
       <c r="G61">
         <v>3.18</v>
@@ -6405,45 +6405,45 @@
         <v>46.5</v>
       </c>
       <c r="M61">
-        <v>13.1901049</v>
+        <v>14.026362</v>
       </c>
       <c r="N61">
-        <v>33.30989510000001</v>
+        <v>32.473638</v>
       </c>
       <c r="O61">
-        <v>4.996484265</v>
+        <v>4.8710457</v>
       </c>
       <c r="P61">
-        <v>28.31341083500001</v>
+        <v>27.6025923</v>
       </c>
       <c r="Q61">
-        <v>45.81341083500001</v>
+        <v>45.1025923</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3058856205837345</v>
+        <v>0.3119490538666795</v>
       </c>
       <c r="T61">
-        <v>1.590651278804106</v>
+        <v>1.627734481957795</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.15</v>
       </c>
       <c r="W61">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.525369991560872</v>
+        <v>3.315186076047374</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6451,22 +6451,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1574706215466718</v>
+        <v>0.1573819886540125</v>
       </c>
       <c r="C62">
-        <v>227.3625164241438</v>
+        <v>224.0674065003083</v>
       </c>
       <c r="D62">
-        <v>443.0025164241438</v>
+        <v>443.3544065003083</v>
       </c>
       <c r="E62">
-        <v>90.62</v>
+        <v>94.267</v>
       </c>
       <c r="F62">
-        <v>218.82</v>
+        <v>222.467</v>
       </c>
       <c r="G62">
         <v>3.18</v>
@@ -6487,28 +6487,28 @@
         <v>46.5</v>
       </c>
       <c r="M62">
-        <v>14.026362</v>
+        <v>14.2601347</v>
       </c>
       <c r="N62">
-        <v>32.473638</v>
+        <v>32.2398653</v>
       </c>
       <c r="O62">
-        <v>4.8710457</v>
+        <v>4.835979794999999</v>
       </c>
       <c r="P62">
-        <v>27.6025923</v>
+        <v>27.403885505</v>
       </c>
       <c r="Q62">
-        <v>45.1025923</v>
+        <v>44.903885505</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3119490538666795</v>
+        <v>0.3183234324461858</v>
       </c>
       <c r="T62">
-        <v>1.627734481957795</v>
+        <v>1.666719387837314</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.315186076047374</v>
+        <v>3.260838763325286</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6533,22 +6533,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1573819886540125</v>
+        <v>0.1572933557613531</v>
       </c>
       <c r="C63">
-        <v>224.0674065003083</v>
+        <v>220.772856054392</v>
       </c>
       <c r="D63">
-        <v>443.3544065003083</v>
+        <v>443.7068560543919</v>
       </c>
       <c r="E63">
-        <v>94.267</v>
+        <v>97.91400000000002</v>
       </c>
       <c r="F63">
-        <v>222.467</v>
+        <v>226.114</v>
       </c>
       <c r="G63">
         <v>3.18</v>
@@ -6569,28 +6569,28 @@
         <v>46.5</v>
       </c>
       <c r="M63">
-        <v>14.2601347</v>
+        <v>14.4939074</v>
       </c>
       <c r="N63">
-        <v>32.2398653</v>
+        <v>32.0060926</v>
       </c>
       <c r="O63">
-        <v>4.835979794999999</v>
+        <v>4.80091389</v>
       </c>
       <c r="P63">
-        <v>27.403885505</v>
+        <v>27.20517871</v>
       </c>
       <c r="Q63">
-        <v>44.903885505</v>
+        <v>44.70517871</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3183234324461858</v>
+        <v>0.3250333046351398</v>
       </c>
       <c r="T63">
-        <v>1.666719387837314</v>
+        <v>1.707756130868387</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.260838763325286</v>
+        <v>3.208244589723265</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6615,22 +6615,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1572933557613531</v>
+        <v>0.1572047228686937</v>
       </c>
       <c r="C64">
-        <v>220.772856054392</v>
+        <v>217.4788664217464</v>
       </c>
       <c r="D64">
-        <v>443.7068560543919</v>
+        <v>444.0598664217464</v>
       </c>
       <c r="E64">
-        <v>97.91400000000002</v>
+        <v>101.561</v>
       </c>
       <c r="F64">
-        <v>226.114</v>
+        <v>229.761</v>
       </c>
       <c r="G64">
         <v>3.18</v>
@@ -6651,28 +6651,28 @@
         <v>46.5</v>
       </c>
       <c r="M64">
-        <v>14.4939074</v>
+        <v>14.7276801</v>
       </c>
       <c r="N64">
-        <v>32.0060926</v>
+        <v>31.7723199</v>
       </c>
       <c r="O64">
-        <v>4.80091389</v>
+        <v>4.765847985</v>
       </c>
       <c r="P64">
-        <v>27.20517871</v>
+        <v>27.006471915</v>
       </c>
       <c r="Q64">
-        <v>44.70517871</v>
+        <v>44.506471915</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3250333046351398</v>
+        <v>0.3321058726180913</v>
       </c>
       <c r="T64">
-        <v>1.707756130868387</v>
+        <v>1.751011076225463</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.208244589723265</v>
+        <v>3.15732007242607</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6697,22 +6697,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1572047228686937</v>
+        <v>0.1571160899760344</v>
       </c>
       <c r="C65">
-        <v>217.4788664217464</v>
+        <v>214.1854389419755</v>
       </c>
       <c r="D65">
-        <v>444.0598664217464</v>
+        <v>444.4134389419755</v>
       </c>
       <c r="E65">
-        <v>101.561</v>
+        <v>105.208</v>
       </c>
       <c r="F65">
-        <v>229.761</v>
+        <v>233.408</v>
       </c>
       <c r="G65">
         <v>3.18</v>
@@ -6733,28 +6733,28 @@
         <v>46.5</v>
       </c>
       <c r="M65">
-        <v>14.7276801</v>
+        <v>14.9614528</v>
       </c>
       <c r="N65">
-        <v>31.7723199</v>
+        <v>31.5385472</v>
       </c>
       <c r="O65">
-        <v>4.765847985</v>
+        <v>4.73078208</v>
       </c>
       <c r="P65">
-        <v>27.006471915</v>
+        <v>26.80776512</v>
       </c>
       <c r="Q65">
-        <v>44.506471915</v>
+        <v>44.30776512</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3321058726180913</v>
+        <v>0.3395713610445401</v>
       </c>
       <c r="T65">
-        <v>1.751011076225463</v>
+        <v>1.796669074102377</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.15732007242607</v>
+        <v>3.107986946294413</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1571160899760344</v>
+        <v>0.1570274570833751</v>
       </c>
       <c r="C66">
-        <v>214.1854389419755</v>
+        <v>210.8925749589536</v>
       </c>
       <c r="D66">
-        <v>444.4134389419755</v>
+        <v>444.7675749589536</v>
       </c>
       <c r="E66">
-        <v>105.208</v>
+        <v>108.855</v>
       </c>
       <c r="F66">
-        <v>233.408</v>
+        <v>237.055</v>
       </c>
       <c r="G66">
         <v>3.18</v>
@@ -6815,28 +6815,28 @@
         <v>46.5</v>
       </c>
       <c r="M66">
-        <v>14.9614528</v>
+        <v>15.1952255</v>
       </c>
       <c r="N66">
-        <v>31.5385472</v>
+        <v>31.3047745</v>
       </c>
       <c r="O66">
-        <v>4.73078208</v>
+        <v>4.695716175</v>
       </c>
       <c r="P66">
-        <v>26.80776512</v>
+        <v>26.609058325</v>
       </c>
       <c r="Q66">
-        <v>44.30776512</v>
+        <v>44.109058325</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3395713610445401</v>
+        <v>0.3474634488096431</v>
       </c>
       <c r="T66">
-        <v>1.796669074102377</v>
+        <v>1.844936100429401</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.107986946294413</v>
+        <v>3.060171762505268</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6861,22 +6861,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1570274570833751</v>
+        <v>0.1569388241907157</v>
       </c>
       <c r="C67">
-        <v>210.8925749589536</v>
+        <v>207.6002758208419</v>
       </c>
       <c r="D67">
-        <v>444.7675749589536</v>
+        <v>445.1222758208419</v>
       </c>
       <c r="E67">
-        <v>108.855</v>
+        <v>112.502</v>
       </c>
       <c r="F67">
-        <v>237.055</v>
+        <v>240.702</v>
       </c>
       <c r="G67">
         <v>3.18</v>
@@ -6897,28 +6897,28 @@
         <v>46.5</v>
       </c>
       <c r="M67">
-        <v>15.1952255</v>
+        <v>15.4289982</v>
       </c>
       <c r="N67">
-        <v>31.3047745</v>
+        <v>31.0710018</v>
       </c>
       <c r="O67">
-        <v>4.695716175</v>
+        <v>4.66065027</v>
       </c>
       <c r="P67">
-        <v>26.609058325</v>
+        <v>26.41035153</v>
       </c>
       <c r="Q67">
-        <v>44.109058325</v>
+        <v>43.91035153</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3474634488096431</v>
+        <v>0.3558197770315169</v>
       </c>
       <c r="T67">
-        <v>1.844936100429401</v>
+        <v>1.896042363599191</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.060171762505268</v>
+        <v>3.013805523679431</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1569388241907157</v>
+        <v>0.1612922912980564</v>
       </c>
       <c r="C68">
-        <v>207.6002758208419</v>
+        <v>187.1744487255372</v>
       </c>
       <c r="D68">
-        <v>445.1222758208419</v>
+        <v>428.3434487255372</v>
       </c>
       <c r="E68">
-        <v>112.502</v>
+        <v>116.149</v>
       </c>
       <c r="F68">
-        <v>240.702</v>
+        <v>244.349</v>
       </c>
       <c r="G68">
         <v>3.18</v>
@@ -6979,45 +6979,45 @@
         <v>46.5</v>
       </c>
       <c r="M68">
-        <v>15.4289982</v>
+        <v>17.5686931</v>
       </c>
       <c r="N68">
-        <v>31.0710018</v>
+        <v>28.9313069</v>
       </c>
       <c r="O68">
-        <v>4.66065027</v>
+        <v>4.339696034999999</v>
       </c>
       <c r="P68">
-        <v>26.41035153</v>
+        <v>24.591610865</v>
       </c>
       <c r="Q68">
-        <v>43.91035153</v>
+        <v>42.09161086499999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3558197770315169</v>
+        <v>0.3646825493880497</v>
       </c>
       <c r="T68">
-        <v>1.896042363599191</v>
+        <v>1.950245976051997</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.15</v>
       </c>
       <c r="W68">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.013805523679431</v>
+        <v>2.646753502683702</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7025,22 +7025,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1612922912980564</v>
+        <v>0.161269958405397</v>
       </c>
       <c r="C69">
-        <v>187.1744487255372</v>
+        <v>183.6102940681167</v>
       </c>
       <c r="D69">
-        <v>428.3434487255372</v>
+        <v>428.4262940681167</v>
       </c>
       <c r="E69">
-        <v>116.149</v>
+        <v>119.796</v>
       </c>
       <c r="F69">
-        <v>244.349</v>
+        <v>247.996</v>
       </c>
       <c r="G69">
         <v>3.18</v>
@@ -7061,28 +7061,28 @@
         <v>46.5</v>
       </c>
       <c r="M69">
-        <v>17.5686931</v>
+        <v>17.8309124</v>
       </c>
       <c r="N69">
-        <v>28.9313069</v>
+        <v>28.6690876</v>
       </c>
       <c r="O69">
-        <v>4.339696034999999</v>
+        <v>4.300363139999999</v>
       </c>
       <c r="P69">
-        <v>24.591610865</v>
+        <v>24.36872446</v>
       </c>
       <c r="Q69">
-        <v>42.09161086499999</v>
+        <v>41.86872446</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3646825493880497</v>
+        <v>0.3740992450168657</v>
       </c>
       <c r="T69">
-        <v>1.950245976051997</v>
+        <v>2.007837314283105</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.646753502683702</v>
+        <v>2.607830657056001</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7107,22 +7107,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.161269958405397</v>
+        <v>0.1612476255127377</v>
       </c>
       <c r="C70">
-        <v>183.6102940681167</v>
+        <v>180.0461714629124</v>
       </c>
       <c r="D70">
-        <v>428.4262940681167</v>
+        <v>428.5091714629124</v>
       </c>
       <c r="E70">
-        <v>119.796</v>
+        <v>123.443</v>
       </c>
       <c r="F70">
-        <v>247.996</v>
+        <v>251.643</v>
       </c>
       <c r="G70">
         <v>3.18</v>
@@ -7143,28 +7143,28 @@
         <v>46.5</v>
       </c>
       <c r="M70">
-        <v>17.8309124</v>
+        <v>18.0931317</v>
       </c>
       <c r="N70">
-        <v>28.6690876</v>
+        <v>28.4068683</v>
       </c>
       <c r="O70">
-        <v>4.300363139999999</v>
+        <v>4.261030245</v>
       </c>
       <c r="P70">
-        <v>24.36872446</v>
+        <v>24.145838055</v>
       </c>
       <c r="Q70">
-        <v>41.86872446</v>
+        <v>41.645838055</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3740992450168657</v>
+        <v>0.3841234693959281</v>
       </c>
       <c r="T70">
-        <v>2.007837314283105</v>
+        <v>2.069144222722671</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.607830657056001</v>
+        <v>2.570036009852291</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7189,22 +7189,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1612476255127377</v>
+        <v>0.1612252926200783</v>
       </c>
       <c r="C71">
-        <v>180.0461714629124</v>
+        <v>176.4820809285296</v>
       </c>
       <c r="D71">
-        <v>428.5091714629124</v>
+        <v>428.5920809285296</v>
       </c>
       <c r="E71">
-        <v>123.443</v>
+        <v>127.09</v>
       </c>
       <c r="F71">
-        <v>251.643</v>
+        <v>255.29</v>
       </c>
       <c r="G71">
         <v>3.18</v>
@@ -7225,28 +7225,28 @@
         <v>46.5</v>
       </c>
       <c r="M71">
-        <v>18.0931317</v>
+        <v>18.355351</v>
       </c>
       <c r="N71">
-        <v>28.4068683</v>
+        <v>28.144649</v>
       </c>
       <c r="O71">
-        <v>4.261030245</v>
+        <v>4.221697349999999</v>
       </c>
       <c r="P71">
-        <v>24.145838055</v>
+        <v>23.92295165</v>
       </c>
       <c r="Q71">
-        <v>41.645838055</v>
+        <v>41.42295165</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3841234693959281</v>
+        <v>0.3948159754002611</v>
       </c>
       <c r="T71">
-        <v>2.069144222722671</v>
+        <v>2.134538258391542</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.570036009852291</v>
+        <v>2.533321209711544</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7271,22 +7271,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1612252926200783</v>
+        <v>0.163556609727419</v>
       </c>
       <c r="C72">
-        <v>176.4820809285296</v>
+        <v>164.3499177376708</v>
       </c>
       <c r="D72">
-        <v>428.5920809285296</v>
+        <v>420.1069177376708</v>
       </c>
       <c r="E72">
-        <v>127.09</v>
+        <v>130.737</v>
       </c>
       <c r="F72">
-        <v>255.29</v>
+        <v>258.937</v>
       </c>
       <c r="G72">
         <v>3.18</v>
@@ -7307,45 +7307,45 @@
         <v>46.5</v>
       </c>
       <c r="M72">
-        <v>18.355351</v>
+        <v>19.6274246</v>
       </c>
       <c r="N72">
-        <v>28.144649</v>
+        <v>26.8725754</v>
       </c>
       <c r="O72">
-        <v>4.221697349999999</v>
+        <v>4.03088631</v>
       </c>
       <c r="P72">
-        <v>23.92295165</v>
+        <v>22.84168909</v>
       </c>
       <c r="Q72">
-        <v>41.42295165</v>
+        <v>40.34168909</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3948159754002611</v>
+        <v>0.4062458956117898</v>
       </c>
       <c r="T72">
-        <v>2.134538258391542</v>
+        <v>2.204442227554817</v>
       </c>
       <c r="U72">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V72">
         <v>0.15</v>
       </c>
       <c r="W72">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.533321209711544</v>
+        <v>2.369134053379576</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7353,22 +7353,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.163556609727419</v>
+        <v>0.1635674268347596</v>
       </c>
       <c r="C73">
-        <v>164.349917737671</v>
+        <v>160.6643303137468</v>
       </c>
       <c r="D73">
-        <v>420.1069177376709</v>
+        <v>420.0683303137468</v>
       </c>
       <c r="E73">
-        <v>130.737</v>
+        <v>134.384</v>
       </c>
       <c r="F73">
-        <v>258.937</v>
+        <v>262.584</v>
       </c>
       <c r="G73">
         <v>3.18</v>
@@ -7389,28 +7389,28 @@
         <v>46.5</v>
       </c>
       <c r="M73">
-        <v>19.6274246</v>
+        <v>19.9038672</v>
       </c>
       <c r="N73">
-        <v>26.8725754</v>
+        <v>26.5961328</v>
       </c>
       <c r="O73">
-        <v>4.030886310000001</v>
+        <v>3.98941992</v>
       </c>
       <c r="P73">
-        <v>22.84168909</v>
+        <v>22.60671288</v>
       </c>
       <c r="Q73">
-        <v>40.34168909</v>
+        <v>40.10671288</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4062458956117895</v>
+        <v>0.4184922386955701</v>
       </c>
       <c r="T73">
-        <v>2.204442227554816</v>
+        <v>2.279339337372611</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.369134053379576</v>
+        <v>2.336229413749304</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7435,22 +7435,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1635674268347596</v>
+        <v>0.1635782439421003</v>
       </c>
       <c r="C74">
-        <v>160.6643303137468</v>
+        <v>156.9787499777924</v>
       </c>
       <c r="D74">
-        <v>420.0683303137468</v>
+        <v>420.0297499777924</v>
       </c>
       <c r="E74">
-        <v>134.384</v>
+        <v>138.031</v>
       </c>
       <c r="F74">
-        <v>262.584</v>
+        <v>266.231</v>
       </c>
       <c r="G74">
         <v>3.18</v>
@@ -7471,28 +7471,28 @@
         <v>46.5</v>
       </c>
       <c r="M74">
-        <v>19.9038672</v>
+        <v>20.1803098</v>
       </c>
       <c r="N74">
-        <v>26.5961328</v>
+        <v>26.3196902</v>
       </c>
       <c r="O74">
-        <v>3.98941992</v>
+        <v>3.94795353</v>
       </c>
       <c r="P74">
-        <v>22.60671288</v>
+        <v>22.37173667</v>
       </c>
       <c r="Q74">
-        <v>40.10671288</v>
+        <v>39.87173667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4184922386955701</v>
+        <v>0.4316457183040751</v>
       </c>
       <c r="T74">
-        <v>2.279339337372611</v>
+        <v>2.359784381250984</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.336229413749304</v>
+        <v>2.304226271095204</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7517,22 +7517,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1635782439421003</v>
+        <v>0.1635890610494409</v>
       </c>
       <c r="C75">
-        <v>156.9787499777924</v>
+        <v>153.2931767278548</v>
       </c>
       <c r="D75">
-        <v>420.0297499777924</v>
+        <v>419.9911767278547</v>
       </c>
       <c r="E75">
-        <v>138.031</v>
+        <v>141.678</v>
       </c>
       <c r="F75">
-        <v>266.231</v>
+        <v>269.878</v>
       </c>
       <c r="G75">
         <v>3.18</v>
@@ -7553,28 +7553,28 @@
         <v>46.5</v>
       </c>
       <c r="M75">
-        <v>20.1803098</v>
+        <v>20.4567524</v>
       </c>
       <c r="N75">
-        <v>26.3196902</v>
+        <v>26.0432476</v>
       </c>
       <c r="O75">
-        <v>3.94795353</v>
+        <v>3.90648714</v>
       </c>
       <c r="P75">
-        <v>22.37173667</v>
+        <v>22.13676046</v>
       </c>
       <c r="Q75">
-        <v>39.87173667</v>
+        <v>39.63676046</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4316457183040751</v>
+        <v>0.4458110040363113</v>
       </c>
       <c r="T75">
-        <v>2.359784381250984</v>
+        <v>2.446417505427692</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.304226271095204</v>
+        <v>2.273088078242566</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7599,22 +7599,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1635890610494409</v>
+        <v>0.1635998781567816</v>
       </c>
       <c r="C76">
-        <v>153.2931767278548</v>
+        <v>149.6076105619821</v>
       </c>
       <c r="D76">
-        <v>419.9911767278547</v>
+        <v>419.9526105619821</v>
       </c>
       <c r="E76">
-        <v>141.678</v>
+        <v>145.325</v>
       </c>
       <c r="F76">
-        <v>269.878</v>
+        <v>273.525</v>
       </c>
       <c r="G76">
         <v>3.18</v>
@@ -7635,28 +7635,28 @@
         <v>46.5</v>
       </c>
       <c r="M76">
-        <v>20.4567524</v>
+        <v>20.733195</v>
       </c>
       <c r="N76">
-        <v>26.0432476</v>
+        <v>25.766805</v>
       </c>
       <c r="O76">
-        <v>3.90648714</v>
+        <v>3.86502075</v>
       </c>
       <c r="P76">
-        <v>22.13676046</v>
+        <v>21.90178425</v>
       </c>
       <c r="Q76">
-        <v>39.63676046</v>
+        <v>39.40178425000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4458110040363113</v>
+        <v>0.4611095126271263</v>
       </c>
       <c r="T76">
-        <v>2.446417505427692</v>
+        <v>2.539981279538538</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.273088078242566</v>
+        <v>2.242780237199332</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7681,22 +7681,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1635998781567816</v>
+        <v>0.1636106952641223</v>
       </c>
       <c r="C77">
-        <v>149.6076105619821</v>
+        <v>145.9220514782226</v>
       </c>
       <c r="D77">
-        <v>419.9526105619821</v>
+        <v>419.9140514782226</v>
       </c>
       <c r="E77">
-        <v>145.325</v>
+        <v>148.972</v>
       </c>
       <c r="F77">
-        <v>273.525</v>
+        <v>277.172</v>
       </c>
       <c r="G77">
         <v>3.18</v>
@@ -7717,28 +7717,28 @@
         <v>46.5</v>
       </c>
       <c r="M77">
-        <v>20.733195</v>
+        <v>21.0096376</v>
       </c>
       <c r="N77">
-        <v>25.766805</v>
+        <v>25.4903624</v>
       </c>
       <c r="O77">
-        <v>3.86502075</v>
+        <v>3.82355436</v>
       </c>
       <c r="P77">
-        <v>21.90178425</v>
+        <v>21.66680804</v>
       </c>
       <c r="Q77">
-        <v>39.40178425000001</v>
+        <v>39.16680804000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4611095126271263</v>
+        <v>0.4776828969338426</v>
       </c>
       <c r="T77">
-        <v>2.539981279538538</v>
+        <v>2.641342034825287</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.242780237199332</v>
+        <v>2.213269970920393</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7763,22 +7763,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1636106952641223</v>
+        <v>0.1636215123714629</v>
       </c>
       <c r="C78">
-        <v>145.9220514782226</v>
+        <v>142.2364994746261</v>
       </c>
       <c r="D78">
-        <v>419.9140514782226</v>
+        <v>419.8754994746261</v>
       </c>
       <c r="E78">
-        <v>148.972</v>
+        <v>152.619</v>
       </c>
       <c r="F78">
-        <v>277.172</v>
+        <v>280.819</v>
       </c>
       <c r="G78">
         <v>3.18</v>
@@ -7799,28 +7799,28 @@
         <v>46.5</v>
       </c>
       <c r="M78">
-        <v>21.0096376</v>
+        <v>21.2860802</v>
       </c>
       <c r="N78">
-        <v>25.4903624</v>
+        <v>25.2139198</v>
       </c>
       <c r="O78">
-        <v>3.82355436</v>
+        <v>3.782087969999999</v>
       </c>
       <c r="P78">
-        <v>21.66680804</v>
+        <v>21.43183183</v>
       </c>
       <c r="Q78">
-        <v>39.16680804000001</v>
+        <v>38.93183182999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4776828969338426</v>
+        <v>0.4956974450933169</v>
       </c>
       <c r="T78">
-        <v>2.641342034825287</v>
+        <v>2.751516768832623</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.213269970920393</v>
+        <v>2.184526205064284</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7845,22 +7845,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1636215123714629</v>
+        <v>0.1636323294788035</v>
       </c>
       <c r="C79">
-        <v>142.2364994746261</v>
+        <v>138.5509545492426</v>
       </c>
       <c r="D79">
-        <v>419.8754994746261</v>
+        <v>419.8369545492426</v>
       </c>
       <c r="E79">
-        <v>152.619</v>
+        <v>156.266</v>
       </c>
       <c r="F79">
-        <v>280.819</v>
+        <v>284.466</v>
       </c>
       <c r="G79">
         <v>3.18</v>
@@ -7881,28 +7881,28 @@
         <v>46.5</v>
       </c>
       <c r="M79">
-        <v>21.2860802</v>
+        <v>21.5625228</v>
       </c>
       <c r="N79">
-        <v>25.2139198</v>
+        <v>24.9374772</v>
       </c>
       <c r="O79">
-        <v>3.782087969999999</v>
+        <v>3.740621579999999</v>
       </c>
       <c r="P79">
-        <v>21.43183183</v>
+        <v>21.19685562</v>
       </c>
       <c r="Q79">
-        <v>38.93183182999999</v>
+        <v>38.69685561999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4956974450933169</v>
+        <v>0.5153496794491069</v>
       </c>
       <c r="T79">
-        <v>2.751516768832623</v>
+        <v>2.871707387749717</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.184526205064284</v>
+        <v>2.156519458845511</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7927,22 +7927,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1636323294788035</v>
+        <v>0.1636431465861442</v>
       </c>
       <c r="C80">
-        <v>138.5509545492426</v>
+        <v>134.865416700123</v>
       </c>
       <c r="D80">
-        <v>419.8369545492426</v>
+        <v>419.798416700123</v>
       </c>
       <c r="E80">
-        <v>156.266</v>
+        <v>159.913</v>
       </c>
       <c r="F80">
-        <v>284.466</v>
+        <v>288.113</v>
       </c>
       <c r="G80">
         <v>3.18</v>
@@ -7963,28 +7963,28 @@
         <v>46.5</v>
       </c>
       <c r="M80">
-        <v>21.5625228</v>
+        <v>21.8389654</v>
       </c>
       <c r="N80">
-        <v>24.9374772</v>
+        <v>24.6610346</v>
       </c>
       <c r="O80">
-        <v>3.740621579999999</v>
+        <v>3.699155189999999</v>
       </c>
       <c r="P80">
-        <v>21.19685562</v>
+        <v>20.96187941</v>
       </c>
       <c r="Q80">
-        <v>38.69685561999999</v>
+        <v>38.46187940999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5153496794491069</v>
+        <v>0.5368735551721151</v>
       </c>
       <c r="T80">
-        <v>2.871707387749717</v>
+        <v>3.003344732277963</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.156519458845511</v>
+        <v>2.129221744176581</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8009,22 +8009,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1636431465861442</v>
+        <v>0.1636539636934848</v>
       </c>
       <c r="C81">
-        <v>134.865416700123</v>
+        <v>131.1798859253186</v>
       </c>
       <c r="D81">
-        <v>419.798416700123</v>
+        <v>419.7598859253186</v>
       </c>
       <c r="E81">
-        <v>159.913</v>
+        <v>163.56</v>
       </c>
       <c r="F81">
-        <v>288.113</v>
+        <v>291.76</v>
       </c>
       <c r="G81">
         <v>3.18</v>
@@ -8045,28 +8045,28 @@
         <v>46.5</v>
       </c>
       <c r="M81">
-        <v>21.8389654</v>
+        <v>22.115408</v>
       </c>
       <c r="N81">
-        <v>24.6610346</v>
+        <v>24.384592</v>
       </c>
       <c r="O81">
-        <v>3.699155189999999</v>
+        <v>3.657688799999999</v>
       </c>
       <c r="P81">
-        <v>20.96187941</v>
+        <v>20.7269032</v>
       </c>
       <c r="Q81">
-        <v>38.46187940999999</v>
+        <v>38.2269032</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5368735551721151</v>
+        <v>0.5605498184674241</v>
       </c>
       <c r="T81">
-        <v>3.003344732277963</v>
+        <v>3.148145811259033</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.129221744176581</v>
+        <v>2.102606472374373</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8091,22 +8091,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1636539636934848</v>
+        <v>0.1636647808008255</v>
       </c>
       <c r="C82">
-        <v>131.1798859253186</v>
+        <v>127.4943622228817</v>
       </c>
       <c r="D82">
-        <v>419.7598859253186</v>
+        <v>419.7213622228817</v>
       </c>
       <c r="E82">
-        <v>163.56</v>
+        <v>167.207</v>
       </c>
       <c r="F82">
-        <v>291.76</v>
+        <v>295.407</v>
       </c>
       <c r="G82">
         <v>3.18</v>
@@ -8127,28 +8127,28 @@
         <v>46.5</v>
       </c>
       <c r="M82">
-        <v>22.115408</v>
+        <v>22.3918506</v>
       </c>
       <c r="N82">
-        <v>24.384592</v>
+        <v>24.1081494</v>
       </c>
       <c r="O82">
-        <v>3.657688799999999</v>
+        <v>3.61622241</v>
       </c>
       <c r="P82">
-        <v>20.7269032</v>
+        <v>20.49192699</v>
       </c>
       <c r="Q82">
-        <v>38.2269032</v>
+        <v>37.99192699</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5605498184674241</v>
+        <v>0.5867183200043448</v>
       </c>
       <c r="T82">
-        <v>3.148145811259033</v>
+        <v>3.308189109080216</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.102606472374373</v>
+        <v>2.076648367777159</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8173,22 +8173,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1636647808008255</v>
+        <v>0.1636755979081661</v>
       </c>
       <c r="C83">
-        <v>127.4943622228817</v>
+        <v>123.8088455908655</v>
       </c>
       <c r="D83">
-        <v>419.7213622228817</v>
+        <v>419.6828455908655</v>
       </c>
       <c r="E83">
-        <v>167.207</v>
+        <v>170.854</v>
       </c>
       <c r="F83">
-        <v>295.407</v>
+        <v>299.054</v>
       </c>
       <c r="G83">
         <v>3.18</v>
@@ -8209,28 +8209,28 @@
         <v>46.5</v>
       </c>
       <c r="M83">
-        <v>22.3918506</v>
+        <v>22.6682932</v>
       </c>
       <c r="N83">
-        <v>24.1081494</v>
+        <v>23.8317068</v>
       </c>
       <c r="O83">
-        <v>3.61622241</v>
+        <v>3.574756019999999</v>
       </c>
       <c r="P83">
-        <v>20.49192699</v>
+        <v>20.25695078</v>
       </c>
       <c r="Q83">
-        <v>37.99192699</v>
+        <v>37.75695078</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5867183200043448</v>
+        <v>0.6157944328231453</v>
       </c>
       <c r="T83">
-        <v>3.308189109080216</v>
+        <v>3.486014995548198</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.076648367777159</v>
+        <v>2.051323387682316</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8255,22 +8255,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1636755979081661</v>
+        <v>0.1636864150155068</v>
       </c>
       <c r="C84">
-        <v>123.8088455908655</v>
+        <v>120.1233360273233</v>
       </c>
       <c r="D84">
-        <v>419.6828455908655</v>
+        <v>419.6443360273233</v>
       </c>
       <c r="E84">
-        <v>170.854</v>
+        <v>174.501</v>
       </c>
       <c r="F84">
-        <v>299.054</v>
+        <v>302.701</v>
       </c>
       <c r="G84">
         <v>3.18</v>
@@ -8291,28 +8291,28 @@
         <v>46.5</v>
       </c>
       <c r="M84">
-        <v>22.6682932</v>
+        <v>22.9447358</v>
       </c>
       <c r="N84">
-        <v>23.8317068</v>
+        <v>23.5552642</v>
       </c>
       <c r="O84">
-        <v>3.574756019999999</v>
+        <v>3.533289629999999</v>
       </c>
       <c r="P84">
-        <v>20.25695078</v>
+        <v>20.02197457</v>
       </c>
       <c r="Q84">
-        <v>37.75695078</v>
+        <v>37.52197457</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6157944328231453</v>
+        <v>0.648291264797099</v>
       </c>
       <c r="T84">
-        <v>3.486014995548198</v>
+        <v>3.684761574541824</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.051323387682316</v>
+        <v>2.026608648071685</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8337,22 +8337,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1636864150155068</v>
+        <v>0.1636972321228474</v>
       </c>
       <c r="C85">
-        <v>120.1233360273233</v>
+        <v>116.4378335303099</v>
       </c>
       <c r="D85">
-        <v>419.6443360273233</v>
+        <v>419.6058335303099</v>
       </c>
       <c r="E85">
-        <v>174.501</v>
+        <v>178.148</v>
       </c>
       <c r="F85">
-        <v>302.701</v>
+        <v>306.348</v>
       </c>
       <c r="G85">
         <v>3.18</v>
@@ -8373,28 +8373,28 @@
         <v>46.5</v>
       </c>
       <c r="M85">
-        <v>22.9447358</v>
+        <v>23.2211784</v>
       </c>
       <c r="N85">
-        <v>23.5552642</v>
+        <v>23.2788216</v>
       </c>
       <c r="O85">
-        <v>3.533289629999999</v>
+        <v>3.49182324</v>
       </c>
       <c r="P85">
-        <v>20.02197457</v>
+        <v>19.78699836</v>
       </c>
       <c r="Q85">
-        <v>37.52197457</v>
+        <v>37.28699836</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.648291264797099</v>
+        <v>0.6848502007677968</v>
       </c>
       <c r="T85">
-        <v>3.684761574541824</v>
+        <v>3.908351475909654</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.026608648071685</v>
+        <v>2.00248235464226</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8419,22 +8419,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1636972321228474</v>
+        <v>0.1739675492301881</v>
       </c>
       <c r="C86">
-        <v>116.4378335303099</v>
+        <v>79.16699507564402</v>
       </c>
       <c r="D86">
-        <v>419.6058335303099</v>
+        <v>385.981995075644</v>
       </c>
       <c r="E86">
-        <v>178.148</v>
+        <v>181.795</v>
       </c>
       <c r="F86">
-        <v>306.348</v>
+        <v>309.995</v>
       </c>
       <c r="G86">
         <v>3.18</v>
@@ -8455,45 +8455,45 @@
         <v>46.5</v>
       </c>
       <c r="M86">
-        <v>23.2211784</v>
+        <v>27.89955</v>
       </c>
       <c r="N86">
-        <v>23.2788216</v>
+        <v>18.60045</v>
       </c>
       <c r="O86">
-        <v>3.49182324</v>
+        <v>2.7900675</v>
       </c>
       <c r="P86">
-        <v>19.78699836</v>
+        <v>15.8103825</v>
       </c>
       <c r="Q86">
-        <v>37.28699836</v>
+        <v>33.3103825</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6848502007677963</v>
+        <v>0.7262836615345872</v>
       </c>
       <c r="T86">
-        <v>3.908351475909651</v>
+        <v>4.161753364126525</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.15</v>
       </c>
       <c r="W86">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.002482354642261</v>
+        <v>1.66669354882068</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8501,22 +8501,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1739675492301881</v>
+        <v>0.1740990663375288</v>
       </c>
       <c r="C87">
-        <v>79.16699507564402</v>
+        <v>75.12433174833365</v>
       </c>
       <c r="D87">
-        <v>385.981995075644</v>
+        <v>385.5863317483336</v>
       </c>
       <c r="E87">
-        <v>181.795</v>
+        <v>185.442</v>
       </c>
       <c r="F87">
-        <v>309.995</v>
+        <v>313.642</v>
       </c>
       <c r="G87">
         <v>3.18</v>
@@ -8537,28 +8537,28 @@
         <v>46.5</v>
       </c>
       <c r="M87">
-        <v>27.89955</v>
+        <v>28.22778</v>
       </c>
       <c r="N87">
-        <v>18.60045</v>
+        <v>18.27222</v>
       </c>
       <c r="O87">
-        <v>2.7900675</v>
+        <v>2.740833</v>
       </c>
       <c r="P87">
-        <v>15.8103825</v>
+        <v>15.531387</v>
       </c>
       <c r="Q87">
-        <v>33.3103825</v>
+        <v>33.031387</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7262836615345872</v>
+        <v>0.7736361881252052</v>
       </c>
       <c r="T87">
-        <v>4.161753364126525</v>
+        <v>4.451355522088664</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.66669354882068</v>
+        <v>1.647313391276253</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8583,22 +8583,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1740990663375288</v>
+        <v>0.1742305834448694</v>
       </c>
       <c r="C88">
-        <v>75.12433174833365</v>
+        <v>71.08247876533375</v>
       </c>
       <c r="D88">
-        <v>385.5863317483336</v>
+        <v>385.1914787653337</v>
       </c>
       <c r="E88">
-        <v>185.442</v>
+        <v>189.089</v>
       </c>
       <c r="F88">
-        <v>313.642</v>
+        <v>317.289</v>
       </c>
       <c r="G88">
         <v>3.18</v>
@@ -8619,28 +8619,28 @@
         <v>46.5</v>
       </c>
       <c r="M88">
-        <v>28.22778</v>
+        <v>28.55601</v>
       </c>
       <c r="N88">
-        <v>18.27222</v>
+        <v>17.94399</v>
       </c>
       <c r="O88">
-        <v>2.740833</v>
+        <v>2.6915985</v>
       </c>
       <c r="P88">
-        <v>15.531387</v>
+        <v>15.2523915</v>
       </c>
       <c r="Q88">
-        <v>33.031387</v>
+        <v>32.7523915</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7736361881252052</v>
+        <v>0.8282737188066874</v>
       </c>
       <c r="T88">
-        <v>4.451355522088664</v>
+        <v>4.785511858198826</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.647313391276253</v>
+        <v>1.628378754594917</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8665,22 +8665,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1742305834448694</v>
+        <v>0.17436210055221</v>
       </c>
       <c r="C89">
-        <v>71.08247876533375</v>
+        <v>67.04143363973378</v>
       </c>
       <c r="D89">
-        <v>385.1914787653337</v>
+        <v>384.7974336397338</v>
       </c>
       <c r="E89">
-        <v>189.089</v>
+        <v>192.736</v>
       </c>
       <c r="F89">
-        <v>317.289</v>
+        <v>320.936</v>
       </c>
       <c r="G89">
         <v>3.18</v>
@@ -8701,28 +8701,28 @@
         <v>46.5</v>
       </c>
       <c r="M89">
-        <v>28.55601</v>
+        <v>28.88424</v>
       </c>
       <c r="N89">
-        <v>17.94399</v>
+        <v>17.61576</v>
       </c>
       <c r="O89">
-        <v>2.6915985</v>
+        <v>2.642364</v>
       </c>
       <c r="P89">
-        <v>15.2523915</v>
+        <v>14.973396</v>
       </c>
       <c r="Q89">
-        <v>32.7523915</v>
+        <v>32.473396</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8282737188066874</v>
+        <v>0.8920175046017503</v>
       </c>
       <c r="T89">
-        <v>4.785511858198826</v>
+        <v>5.175360916994016</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.628378754594917</v>
+        <v>1.609874450565429</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8747,22 +8747,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.17436210055221</v>
+        <v>0.1744936176595507</v>
       </c>
       <c r="C90">
-        <v>67.04143363973378</v>
+        <v>63.00119389478954</v>
       </c>
       <c r="D90">
-        <v>384.7974336397338</v>
+        <v>384.4041938947895</v>
       </c>
       <c r="E90">
-        <v>192.736</v>
+        <v>196.383</v>
       </c>
       <c r="F90">
-        <v>320.936</v>
+        <v>324.583</v>
       </c>
       <c r="G90">
         <v>3.18</v>
@@ -8783,28 +8783,28 @@
         <v>46.5</v>
       </c>
       <c r="M90">
-        <v>28.88424</v>
+        <v>29.21247</v>
       </c>
       <c r="N90">
-        <v>17.61576</v>
+        <v>17.28753</v>
       </c>
       <c r="O90">
-        <v>2.642364</v>
+        <v>2.5931295</v>
       </c>
       <c r="P90">
-        <v>14.973396</v>
+        <v>14.6944005</v>
       </c>
       <c r="Q90">
-        <v>32.473396</v>
+        <v>32.1944005</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8920175046017503</v>
+        <v>0.967351069632279</v>
       </c>
       <c r="T90">
-        <v>5.175360916994016</v>
+        <v>5.636091622842876</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.609874450565429</v>
+        <v>1.591785973592784</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8829,22 +8829,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1744936176595507</v>
+        <v>0.1746251347668913</v>
       </c>
       <c r="C91">
-        <v>63.00119389478954</v>
+        <v>58.96175706387015</v>
       </c>
       <c r="D91">
-        <v>384.4041938947895</v>
+        <v>384.0117570638702</v>
       </c>
       <c r="E91">
-        <v>196.383</v>
+        <v>200.03</v>
       </c>
       <c r="F91">
-        <v>324.583</v>
+        <v>328.23</v>
       </c>
       <c r="G91">
         <v>3.18</v>
@@ -8865,28 +8865,28 @@
         <v>46.5</v>
       </c>
       <c r="M91">
-        <v>29.21247</v>
+        <v>29.5407</v>
       </c>
       <c r="N91">
-        <v>17.28753</v>
+        <v>16.9593</v>
       </c>
       <c r="O91">
-        <v>2.5931295</v>
+        <v>2.543895</v>
       </c>
       <c r="P91">
-        <v>14.6944005</v>
+        <v>14.415405</v>
       </c>
       <c r="Q91">
-        <v>32.1944005</v>
+        <v>31.915405</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.967351069632279</v>
+        <v>1.057751347668914</v>
       </c>
       <c r="T91">
-        <v>5.636091622842876</v>
+        <v>6.188968469861509</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.591785973592784</v>
+        <v>1.574099462775087</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8911,22 +8911,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1746251347668913</v>
+        <v>0.174756651874232</v>
       </c>
       <c r="C92">
-        <v>58.96175706387015</v>
+        <v>54.92312069040804</v>
       </c>
       <c r="D92">
-        <v>384.0117570638702</v>
+        <v>383.620120690408</v>
       </c>
       <c r="E92">
-        <v>200.03</v>
+        <v>203.677</v>
       </c>
       <c r="F92">
-        <v>328.23</v>
+        <v>331.877</v>
       </c>
       <c r="G92">
         <v>3.18</v>
@@ -8947,28 +8947,28 @@
         <v>46.5</v>
       </c>
       <c r="M92">
-        <v>29.5407</v>
+        <v>29.86893</v>
       </c>
       <c r="N92">
-        <v>16.9593</v>
+        <v>16.63107</v>
       </c>
       <c r="O92">
-        <v>2.543895</v>
+        <v>2.4946605</v>
       </c>
       <c r="P92">
-        <v>14.415405</v>
+        <v>14.1364095</v>
       </c>
       <c r="Q92">
-        <v>31.915405</v>
+        <v>31.6364095</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.057751347668914</v>
+        <v>1.168240576380356</v>
       </c>
       <c r="T92">
-        <v>6.188968469861509</v>
+        <v>6.864706838439837</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.574099462775087</v>
+        <v>1.556801666480855</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8993,22 +8993,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.174756651874232</v>
+        <v>0.1748881689815727</v>
       </c>
       <c r="C93">
-        <v>54.92312069040804</v>
+        <v>50.88528232784608</v>
       </c>
       <c r="D93">
-        <v>383.620120690408</v>
+        <v>383.2292823278461</v>
       </c>
       <c r="E93">
-        <v>203.677</v>
+        <v>207.324</v>
       </c>
       <c r="F93">
-        <v>331.877</v>
+        <v>335.524</v>
       </c>
       <c r="G93">
         <v>3.18</v>
@@ -9029,28 +9029,28 @@
         <v>46.5</v>
       </c>
       <c r="M93">
-        <v>29.86893</v>
+        <v>30.19716</v>
       </c>
       <c r="N93">
-        <v>16.63107</v>
+        <v>16.30284</v>
       </c>
       <c r="O93">
-        <v>2.4946605</v>
+        <v>2.445426</v>
       </c>
       <c r="P93">
-        <v>14.1364095</v>
+        <v>13.857414</v>
       </c>
       <c r="Q93">
-        <v>31.6364095</v>
+        <v>31.357414</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.168240576380356</v>
+        <v>1.306352112269659</v>
       </c>
       <c r="T93">
-        <v>6.864706838439837</v>
+        <v>7.70937979916275</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.556801666480855</v>
+        <v>1.539879909236498</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9075,22 +9075,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1748881689815727</v>
+        <v>0.1750196860889133</v>
       </c>
       <c r="C94">
-        <v>50.88528232784608</v>
+        <v>46.84823953958784</v>
       </c>
       <c r="D94">
-        <v>383.2292823278461</v>
+        <v>382.8392395395878</v>
       </c>
       <c r="E94">
-        <v>207.324</v>
+        <v>210.971</v>
       </c>
       <c r="F94">
-        <v>335.524</v>
+        <v>339.171</v>
       </c>
       <c r="G94">
         <v>3.18</v>
@@ -9111,28 +9111,28 @@
         <v>46.5</v>
       </c>
       <c r="M94">
-        <v>30.19716</v>
+        <v>30.52539</v>
       </c>
       <c r="N94">
-        <v>16.30284</v>
+        <v>15.97461</v>
       </c>
       <c r="O94">
-        <v>2.445426</v>
+        <v>2.3961915</v>
       </c>
       <c r="P94">
-        <v>13.857414</v>
+        <v>13.5784185</v>
       </c>
       <c r="Q94">
-        <v>31.357414</v>
+        <v>31.0784185</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.306352112269659</v>
+        <v>1.483924086984477</v>
       </c>
       <c r="T94">
-        <v>7.70937979916275</v>
+        <v>8.795387891520779</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.539879909236498</v>
+        <v>1.523322060750084</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9157,22 +9157,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1750196860889133</v>
+        <v>0.1751512031962539</v>
       </c>
       <c r="C95">
-        <v>46.84823953958784</v>
+        <v>42.81198989894591</v>
       </c>
       <c r="D95">
-        <v>382.8392395395878</v>
+        <v>382.4499898989459</v>
       </c>
       <c r="E95">
-        <v>210.971</v>
+        <v>214.618</v>
       </c>
       <c r="F95">
-        <v>339.171</v>
+        <v>342.818</v>
       </c>
       <c r="G95">
         <v>3.18</v>
@@ -9193,28 +9193,28 @@
         <v>46.5</v>
       </c>
       <c r="M95">
-        <v>30.52539</v>
+        <v>30.85362</v>
       </c>
       <c r="N95">
-        <v>15.97461</v>
+        <v>15.64638</v>
       </c>
       <c r="O95">
-        <v>2.3961915</v>
+        <v>2.346957000000001</v>
       </c>
       <c r="P95">
-        <v>13.5784185</v>
+        <v>13.299423</v>
       </c>
       <c r="Q95">
-        <v>31.0784185</v>
+        <v>30.799423</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.483924086984477</v>
+        <v>1.720686719937567</v>
       </c>
       <c r="T95">
-        <v>8.795387891520779</v>
+        <v>10.24339868133148</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.523322060750084</v>
+        <v>1.507116506912317</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9239,22 +9239,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1751512031962539</v>
+        <v>0.2243718495136481</v>
       </c>
       <c r="C96">
-        <v>42.81198989894591</v>
+        <v>-66.25160145168718</v>
       </c>
       <c r="D96">
-        <v>382.4499898989459</v>
+        <v>277.0333985483128</v>
       </c>
       <c r="E96">
-        <v>214.618</v>
+        <v>218.265</v>
       </c>
       <c r="F96">
-        <v>342.818</v>
+        <v>346.465</v>
       </c>
       <c r="G96">
         <v>3.18</v>
@@ -9275,45 +9275,45 @@
         <v>46.5</v>
       </c>
       <c r="M96">
-        <v>30.85362</v>
+        <v>50.86106200000001</v>
       </c>
       <c r="N96">
-        <v>15.64638</v>
+        <v>-4.361062000000011</v>
       </c>
       <c r="O96">
-        <v>2.346957000000001</v>
+        <v>-0.6541593000000017</v>
       </c>
       <c r="P96">
-        <v>13.299423</v>
+        <v>-3.706902700000009</v>
       </c>
       <c r="Q96">
-        <v>30.799423</v>
+        <v>13.79309729999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.720686719937567</v>
+        <v>2.08074315972731</v>
       </c>
       <c r="T96">
-        <v>10.24339868133148</v>
+        <v>12.44545904555997</v>
       </c>
       <c r="U96">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.15</v>
+        <v>0.1371383082799175</v>
       </c>
       <c r="W96">
-        <v>0.0765</v>
+        <v>0.1266680963445081</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.507116506912317</v>
+        <v>0.9142553885327835</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9321,22 +9321,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2243718495136481</v>
+        <v>0.2253818495136481</v>
       </c>
       <c r="C97">
-        <v>-66.25160145168718</v>
+        <v>-71.45668615396403</v>
       </c>
       <c r="D97">
-        <v>277.0333985483128</v>
+        <v>275.475313846036</v>
       </c>
       <c r="E97">
-        <v>218.265</v>
+        <v>221.912</v>
       </c>
       <c r="F97">
-        <v>346.465</v>
+        <v>350.112</v>
       </c>
       <c r="G97">
         <v>3.18</v>
@@ -9357,37 +9357,37 @@
         <v>46.5</v>
       </c>
       <c r="M97">
-        <v>50.86106200000001</v>
+        <v>51.39644160000001</v>
       </c>
       <c r="N97">
-        <v>-4.361062000000011</v>
+        <v>-4.89644160000001</v>
       </c>
       <c r="O97">
-        <v>-0.6541593000000017</v>
+        <v>-0.7344662400000015</v>
       </c>
       <c r="P97">
-        <v>-3.706902700000009</v>
+        <v>-4.161975360000008</v>
       </c>
       <c r="Q97">
-        <v>13.79309729999999</v>
+        <v>13.33802463999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.08074315972731</v>
+        <v>2.58947894965914</v>
       </c>
       <c r="T97">
-        <v>12.44545904555997</v>
+        <v>15.55682380694997</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1371383082799175</v>
+        <v>0.1357097842353351</v>
       </c>
       <c r="W97">
-        <v>0.1266680963445081</v>
+        <v>0.1268778036742528</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9142553885327835</v>
+        <v>0.9047318949022337</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9403,22 +9403,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2253818495136481</v>
+        <v>0.2263918495136482</v>
       </c>
       <c r="C98">
-        <v>-71.45668615396403</v>
+        <v>-76.64434298722534</v>
       </c>
       <c r="D98">
-        <v>275.4753138460359</v>
+        <v>273.9346570127746</v>
       </c>
       <c r="E98">
-        <v>221.912</v>
+        <v>225.559</v>
       </c>
       <c r="F98">
-        <v>350.112</v>
+        <v>353.759</v>
       </c>
       <c r="G98">
         <v>3.18</v>
@@ -9439,37 +9439,37 @@
         <v>46.5</v>
       </c>
       <c r="M98">
-        <v>51.3964416</v>
+        <v>51.9318212</v>
       </c>
       <c r="N98">
-        <v>-4.896441600000003</v>
+        <v>-5.431821200000002</v>
       </c>
       <c r="O98">
-        <v>-0.7344662400000004</v>
+        <v>-0.8147731800000002</v>
       </c>
       <c r="P98">
-        <v>-4.161975360000002</v>
+        <v>-4.617048020000001</v>
       </c>
       <c r="Q98">
-        <v>13.33802464</v>
+        <v>12.88295198</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.589478949659133</v>
+        <v>3.437371932878845</v>
       </c>
       <c r="T98">
-        <v>15.55682380694993</v>
+        <v>20.7424317425999</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1357097842353351</v>
+        <v>0.1343107142947646</v>
       </c>
       <c r="W98">
-        <v>0.1268778036742528</v>
+        <v>0.1270831871415286</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9047318949022338</v>
+        <v>0.8954047619650974</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9485,22 +9485,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2263918495136482</v>
+        <v>0.2274018495136481</v>
       </c>
       <c r="C99">
-        <v>-76.64434298722534</v>
+        <v>-81.814862732888</v>
       </c>
       <c r="D99">
-        <v>273.9346570127746</v>
+        <v>272.411137267112</v>
       </c>
       <c r="E99">
-        <v>225.559</v>
+        <v>229.206</v>
       </c>
       <c r="F99">
-        <v>353.759</v>
+        <v>357.406</v>
       </c>
       <c r="G99">
         <v>3.18</v>
@@ -9521,37 +9521,37 @@
         <v>46.5</v>
       </c>
       <c r="M99">
-        <v>51.9318212</v>
+        <v>52.46720080000001</v>
       </c>
       <c r="N99">
-        <v>-5.431821200000002</v>
+        <v>-5.967200800000008</v>
       </c>
       <c r="O99">
-        <v>-0.8147731800000002</v>
+        <v>-0.8950801200000011</v>
       </c>
       <c r="P99">
-        <v>-4.617048020000001</v>
+        <v>-5.072120680000006</v>
       </c>
       <c r="Q99">
-        <v>12.88295198</v>
+        <v>12.42787931999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.437371932878845</v>
+        <v>5.133157899318267</v>
       </c>
       <c r="T99">
-        <v>20.7424317425999</v>
+        <v>31.11364761389985</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1343107142947646</v>
+        <v>0.1329401968019609</v>
       </c>
       <c r="W99">
-        <v>0.1270831871415286</v>
+        <v>0.1272843791094722</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8954047619650974</v>
+        <v>0.8862679786797392</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9567,22 +9567,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2274018495136481</v>
+        <v>0.2284118495136481</v>
       </c>
       <c r="C100">
-        <v>-81.814862732888</v>
+        <v>-86.96852973928736</v>
       </c>
       <c r="D100">
-        <v>272.411137267112</v>
+        <v>270.9044702607126</v>
       </c>
       <c r="E100">
-        <v>229.206</v>
+        <v>232.853</v>
       </c>
       <c r="F100">
-        <v>357.406</v>
+        <v>361.053</v>
       </c>
       <c r="G100">
         <v>3.18</v>
@@ -9603,37 +9603,37 @@
         <v>46.5</v>
       </c>
       <c r="M100">
-        <v>52.46720080000001</v>
+        <v>53.00258040000001</v>
       </c>
       <c r="N100">
-        <v>-5.967200800000008</v>
+        <v>-6.502580400000006</v>
       </c>
       <c r="O100">
-        <v>-0.8950801200000011</v>
+        <v>-0.975387060000001</v>
       </c>
       <c r="P100">
-        <v>-5.072120680000006</v>
+        <v>-5.527193340000006</v>
       </c>
       <c r="Q100">
-        <v>12.42787931999999</v>
+        <v>11.97280665999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.133157899318267</v>
+        <v>10.22051579863653</v>
       </c>
       <c r="T100">
-        <v>31.11364761389985</v>
+        <v>62.2272952277997</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1329401968019609</v>
+        <v>0.131597366531234</v>
       </c>
       <c r="W100">
-        <v>0.1272843791094722</v>
+        <v>0.1274815065932149</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9641,91 +9641,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8862679786797392</v>
+        <v>0.8773157768748934</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2284118495136481</v>
-      </c>
-      <c r="C101">
-        <v>-86.96852973928736</v>
-      </c>
-      <c r="D101">
-        <v>270.9044702607126</v>
-      </c>
-      <c r="E101">
-        <v>232.853</v>
-      </c>
-      <c r="F101">
-        <v>361.053</v>
-      </c>
-      <c r="G101">
-        <v>3.18</v>
-      </c>
-      <c r="H101">
-        <v>236.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>64</v>
-      </c>
-      <c r="K101">
-        <v>17.5</v>
-      </c>
-      <c r="L101">
-        <v>46.5</v>
-      </c>
-      <c r="M101">
-        <v>53.00258040000001</v>
-      </c>
-      <c r="N101">
-        <v>-6.502580400000006</v>
-      </c>
-      <c r="O101">
-        <v>-0.975387060000001</v>
-      </c>
-      <c r="P101">
-        <v>-5.527193340000006</v>
-      </c>
-      <c r="Q101">
-        <v>11.97280665999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.22051579863653</v>
-      </c>
-      <c r="T101">
-        <v>62.2272952277997</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.131597366531234</v>
-      </c>
-      <c r="W101">
-        <v>0.1274815065932149</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8773157768748934</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
